--- a/docs/damping_curve_MRAx0.xlsx
+++ b/docs/damping_curve_MRAx0.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="115">
   <si>
     <t>Astral · LSC Sweep</t>
   </si>
@@ -299,6 +299,93 @@
     <t>Astral · HSC Sweep</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>CTM Racing · MRAx0 · Damping Calculator</t>
+  </si>
+  <si>
+    <t>MRA60 / MRA80 · 柏油拉力 · c / C / R 调节与阻尼力计算</t>
+  </si>
+  <si>
+    <t>适用车型</t>
+  </si>
+  <si>
+    <t>当前曲线参数</t>
+  </si>
+  <si>
+    <t>HSbump · 高速增量</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · Valving Parameters</t>
+  </si>
+  <si>
+    <t>MRA60 / MRA60 (Mod) / MRA80 · 柏油拉力系列；黄色单元格为可编辑标定。</t>
+  </si>
+  <si>
+    <t>HSbump · 高速增量</t>
+  </si>
+  <si>
+    <t>LSR · R（MRA60）</t>
+  </si>
+  <si>
+    <t>Adjusters · 调节格数</t>
+  </si>
+  <si>
+    <t>LSC · 全系列</t>
+  </si>
+  <si>
+    <t>HSC · 全系列</t>
+  </si>
+  <si>
+    <t>LSR · MRA60</t>
+  </si>
+  <si>
+    <t>LSR · MRA80</t>
+  </si>
+  <si>
+    <t>Sweep 使用 MRA60 的格数；MRA60 (Mod) 同为 40 格回弹，MRA80 为 60 格，适用车型在计算器选择。</t>
+  </si>
+  <si>
+    <t>Model · 基础阻尼模型</t>
+  </si>
+  <si>
+    <t>理论曲线采用连续分段接续假设；仅计算基础阻尼，不包含气体支撑、弹簧、HBS/HRS 或 LRS/DSV。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · LSC Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · HSC Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · LSR Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · Full Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · LSC Sweep</t>
+  </si>
+  <si>
+    <t>柏油拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · HSC Sweep</t>
+  </si>
+  <si>
+    <t>柏油拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · LSR Sweep</t>
+  </si>
+  <si>
+    <t>柏油拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx0 · Full Sweep</t>
+  </si>
+  <si>
+    <t>柏油拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
 </sst>
 </file>
 
@@ -549,7 +636,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression</a:t>
+              <a:t>MRAx0 · LSC Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1639,7 +1726,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression</a:t>
+              <a:t>MRAx0 · HSC Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2719,7 +2806,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Rebound</a:t>
+              <a:t>MRAx0 · LSR Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3792,7 +3879,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression (+) / Rebound (−)</a:t>
+              <a:t>MRAx0 · Compression (+) / Rebound (−)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -6124,7 +6211,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -6167,7 +6254,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -6200,7 +6287,7 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>47</v>
@@ -6360,7 +6447,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="20" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
@@ -6437,7 +6524,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="22" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -7026,7 +7113,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -7069,7 +7156,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -7790,7 +7877,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -7833,7 +7920,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -8554,7 +8641,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -8597,7 +8684,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -9310,7 +9397,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -9353,7 +9440,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -10070,7 +10157,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -10089,7 +10176,7 @@
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="25" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -10446,7 +10533,7 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>22</v>
@@ -10553,7 +10640,7 @@
     <row r="16" spans="1:15" ht="23" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>19</v>
@@ -10773,7 +10860,7 @@
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="20" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -10792,7 +10879,7 @@
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="22" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C23" s="22"/>
       <c r="D23" s="1">
@@ -10800,7 +10887,7 @@
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="23" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -10815,7 +10902,7 @@
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="22" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="1">
@@ -10836,7 +10923,7 @@
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="22" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="1">
@@ -10857,7 +10944,7 @@
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="22" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="1">
@@ -10897,7 +10984,7 @@
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="20" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -10973,7 +11060,7 @@
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="19" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
@@ -11191,7 +11278,7 @@
     <row r="1" spans="1:22" ht="22" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="28" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
@@ -12884,7 +12971,7 @@
     <row r="41" spans="1:22" ht="22" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="28" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
@@ -14538,7 +14625,7 @@
     </row>
     <row r="81" spans="2:22" ht="22" customHeight="1">
       <c r="B81" s="29" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
@@ -16191,7 +16278,7 @@
     </row>
     <row r="121" spans="2:22" ht="22" customHeight="1">
       <c r="B121" s="29" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>

--- a/docs/damping_curve_MRAx0.xlsx
+++ b/docs/damping_curve_MRAx0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC1C9EF-FA7C-43D1-A667-EC3087A21FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E35C9C-723E-4F64-BADA-4A948CDE19C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -293,9 +293,6 @@
     <t>避震器型号</t>
   </si>
   <si>
-    <t>MRA80 (Mod)</t>
-  </si>
-  <si>
     <t>计算器支持任意非负轴速；Sweep 图显示 0–0.6 m/s。斜率和膝点由所选阀系插值得到。</t>
   </si>
   <si>
@@ -309,6 +306,9 @@
   </si>
   <si>
     <t>Type-B：HSC 控制第一 knee，无 HS 附加阻尼。Type-A：HSC 控制高速增量和第二 knee。</t>
+  </si>
+  <si>
+    <t>MRA60</t>
   </si>
 </sst>
 </file>
@@ -491,31 +491,31 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -666,40 +666,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135</c:v>
+                  <c:v>102.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>405</c:v>
+                  <c:v>307.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>540</c:v>
+                  <c:v>410</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>675</c:v>
+                  <c:v>512.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>810</c:v>
+                  <c:v>615</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>908.55</c:v>
+                  <c:v>717.49999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1007.1000000000001</c:v>
+                  <c:v>920.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1105.6500000000001</c:v>
+                  <c:v>1122.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1204.2</c:v>
+                  <c:v>1325</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1302.75</c:v>
+                  <c:v>1527.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1401.3</c:v>
+                  <c:v>1730</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,40 +794,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>147.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>293.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>436.30499999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>579.38000000000011</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>722.45499999999993</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>865.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1207.8</c:v>
+                  <c:v>1008.6049999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1335.6000000000001</c:v>
+                  <c:v>1251.68</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1463.4</c:v>
+                  <c:v>1494.7549999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1591.2</c:v>
+                  <c:v>1737.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1719</c:v>
+                  <c:v>1980.9050000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1846.8</c:v>
+                  <c:v>2223.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -922,40 +922,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1505.25</c:v>
+                  <c:v>1285.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1660.5</c:v>
+                  <c:v>1566.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1815.75</c:v>
+                  <c:v>1847.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1971</c:v>
+                  <c:v>2127.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2126.25</c:v>
+                  <c:v>2408.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2281.5</c:v>
+                  <c:v>2689.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1050,40 +1050,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270</c:v>
+                  <c:v>237.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>540</c:v>
+                  <c:v>466.45000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>810</c:v>
+                  <c:v>682.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1080</c:v>
+                  <c:v>898.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1350</c:v>
+                  <c:v>1114.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1620</c:v>
+                  <c:v>1330.9499999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1800.8999999999999</c:v>
+                  <c:v>1547.0749999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1981.8000000000002</c:v>
+                  <c:v>1863.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2162.6999999999998</c:v>
+                  <c:v>2179.3250000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2343.6</c:v>
+                  <c:v>2495.4499999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2524.5</c:v>
+                  <c:v>2811.5749999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2705.3999999999996</c:v>
+                  <c:v>3127.7000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,40 +1178,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>315</c:v>
+                  <c:v>282.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>630</c:v>
+                  <c:v>551.44000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>945</c:v>
+                  <c:v>800.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1260</c:v>
+                  <c:v>1048.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1575</c:v>
+                  <c:v>1297.2399999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1890</c:v>
+                  <c:v>1545.84</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2094.75</c:v>
+                  <c:v>1794.4399999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2299.5</c:v>
+                  <c:v>2143.04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2504.25</c:v>
+                  <c:v>2491.64</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2709</c:v>
+                  <c:v>2840.24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2913.75</c:v>
+                  <c:v>3188.84</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3118.5</c:v>
+                  <c:v>3537.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1506,40 +1506,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1055.25</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1210.5</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1365.7499999999998</c:v>
+                  <c:v>1290.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1521</c:v>
+                  <c:v>1496.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1676.25</c:v>
+                  <c:v>1702.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1831.4999999999998</c:v>
+                  <c:v>1907.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1986.75</c:v>
+                  <c:v>2113.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2142</c:v>
+                  <c:v>2319.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1634,40 +1634,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1280.25</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1435.5</c:v>
+                  <c:v>1291.3799999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1590.75</c:v>
+                  <c:v>1534.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1746</c:v>
+                  <c:v>1778.28</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1901.25</c:v>
+                  <c:v>2021.73</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2056.5</c:v>
+                  <c:v>2265.1800000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2211.75</c:v>
+                  <c:v>2508.63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,40 +1762,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1505.25</c:v>
+                  <c:v>1285.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1660.5</c:v>
+                  <c:v>1566.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1815.75</c:v>
+                  <c:v>1847.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1971</c:v>
+                  <c:v>2127.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2126.25</c:v>
+                  <c:v>2408.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2281.5</c:v>
+                  <c:v>2689.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1890,40 +1890,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1575</c:v>
+                  <c:v>1285.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1730.25</c:v>
+                  <c:v>1589.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1885.5</c:v>
+                  <c:v>1908.28</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2040.75</c:v>
+                  <c:v>2226.73</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2196</c:v>
+                  <c:v>2545.1800000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2351.25</c:v>
+                  <c:v>2863.63</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,40 +2018,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1575</c:v>
+                  <c:v>1285.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1800</c:v>
+                  <c:v>1606.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1955.25</c:v>
+                  <c:v>1962.0300000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2110.5</c:v>
+                  <c:v>2317.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2265.75</c:v>
+                  <c:v>2673.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2421</c:v>
+                  <c:v>3029.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3179,40 +3179,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>135</c:v>
+                  <c:v>102.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>405</c:v>
+                  <c:v>307.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>540</c:v>
+                  <c:v>410</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>638.54999999999995</c:v>
+                  <c:v>512.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>737.09999999999991</c:v>
+                  <c:v>615</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>835.64999999999986</c:v>
+                  <c:v>722.49999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>934.2</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1032.75</c:v>
+                  <c:v>977.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1131.3</c:v>
+                  <c:v>1105</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1229.8499999999999</c:v>
+                  <c:v>1232.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1328.4</c:v>
+                  <c:v>1360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3307,40 +3307,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>147.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>293.23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>436.30499999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>579.38000000000011</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>722.45499999999993</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1027.8</c:v>
+                  <c:v>865.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1155.5999999999999</c:v>
+                  <c:v>1014.8549999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1283.4000000000001</c:v>
+                  <c:v>1220.43</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1411.2</c:v>
+                  <c:v>1426.0049999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1539</c:v>
+                  <c:v>1631.58</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1666.8000000000002</c:v>
+                  <c:v>1837.1550000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1794.6</c:v>
+                  <c:v>2042.73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3435,40 +3435,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>225</c:v>
+                  <c:v>192.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>450</c:v>
+                  <c:v>380.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>675</c:v>
+                  <c:v>561.32999999999993</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>900</c:v>
+                  <c:v>742.28</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1125</c:v>
+                  <c:v>923.2299999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1350</c:v>
+                  <c:v>1104.1799999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1505.25</c:v>
+                  <c:v>1285.1299999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1660.5</c:v>
+                  <c:v>1566.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1815.75</c:v>
+                  <c:v>1847.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1971</c:v>
+                  <c:v>2127.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2126.25</c:v>
+                  <c:v>2408.9300000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2281.5</c:v>
+                  <c:v>2689.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3563,40 +3563,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270</c:v>
+                  <c:v>237.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>540</c:v>
+                  <c:v>466.45000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>810</c:v>
+                  <c:v>682.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1080</c:v>
+                  <c:v>898.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1350</c:v>
+                  <c:v>1114.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1620</c:v>
+                  <c:v>1330.9499999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1889.9999999999998</c:v>
+                  <c:v>1547.0749999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2070.9</c:v>
+                  <c:v>1886.9500000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2251.7999999999997</c:v>
+                  <c:v>2240.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2432.6999999999998</c:v>
+                  <c:v>2594.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2613.6</c:v>
+                  <c:v>2947.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2794.4999999999995</c:v>
+                  <c:v>3301.4500000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3691,40 +3691,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>315</c:v>
+                  <c:v>282.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>630</c:v>
+                  <c:v>551.44000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>945</c:v>
+                  <c:v>800.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1260</c:v>
+                  <c:v>1048.6400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1575</c:v>
+                  <c:v>1297.2399999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1890</c:v>
+                  <c:v>1545.84</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2205</c:v>
+                  <c:v>1794.4399999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2520</c:v>
+                  <c:v>2183.04</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2724.75</c:v>
+                  <c:v>2606.64</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2929.5</c:v>
+                  <c:v>3030.24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3134.25</c:v>
+                  <c:v>3453.84</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3339</c:v>
+                  <c:v>3877.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3819,40 +3819,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-162.5</c:v>
+                  <c:v>-115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-325</c:v>
+                  <c:v>-230</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-487.5</c:v>
+                  <c:v>-345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-650</c:v>
+                  <c:v>-460</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-770.9</c:v>
+                  <c:v>-571.31999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-881.4</c:v>
+                  <c:v>-677.11999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-991.9</c:v>
+                  <c:v>-782.92</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1102.4000000000001</c:v>
+                  <c:v>-888.72</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1212.9000000000001</c:v>
+                  <c:v>-994.52</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1323.4</c:v>
+                  <c:v>-1100.3200000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1433.9</c:v>
+                  <c:v>-1206.1200000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1544.4</c:v>
+                  <c:v>-1311.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3947,40 +3947,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-200</c:v>
+                  <c:v>-152.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-400</c:v>
+                  <c:v>-305</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-600</c:v>
+                  <c:v>-457.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-800</c:v>
+                  <c:v>-610</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-951</c:v>
+                  <c:v>-759.14499999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1081</c:v>
+                  <c:v>-894.87</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1211</c:v>
+                  <c:v>-1030.595</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1341</c:v>
+                  <c:v>-1166.3200000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1471</c:v>
+                  <c:v>-1302.0450000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1601</c:v>
+                  <c:v>-1437.77</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1731.0000000000002</c:v>
+                  <c:v>-1573.4950000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1861</c:v>
+                  <c:v>-1709.2199999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4075,40 +4075,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-237.5</c:v>
+                  <c:v>-190</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-475</c:v>
+                  <c:v>-380</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-712.5</c:v>
+                  <c:v>-570</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>-760</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-950</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>-1133.3499999999999</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1280.5999999999999</c:v>
+                  <c:v>-1113.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1427.85</c:v>
+                  <c:v>-1276.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1575.1</c:v>
+                  <c:v>-1440.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1722.35</c:v>
+                  <c:v>-1603.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1869.6</c:v>
+                  <c:v>-1767</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2016.8500000000004</c:v>
+                  <c:v>-1930.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2164.1</c:v>
+                  <c:v>-2093.8000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,40 +4203,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-275</c:v>
+                  <c:v>-227.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-550</c:v>
+                  <c:v>-455</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-825</c:v>
+                  <c:v>-682.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1100</c:v>
+                  <c:v>-910</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1318.625</c:v>
+                  <c:v>-1137.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1480.875</c:v>
+                  <c:v>-1334.06</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1643.125</c:v>
+                  <c:v>-1522.885</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1805.375</c:v>
+                  <c:v>-1711.71</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1967.625</c:v>
+                  <c:v>-1900.5350000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2129.875</c:v>
+                  <c:v>-2089.36</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2292.1250000000005</c:v>
+                  <c:v>-2278.1850000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2454.375</c:v>
+                  <c:v>-2467.0100000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4331,40 +4331,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-312.5</c:v>
+                  <c:v>-265</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-625</c:v>
+                  <c:v>-530</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-937.5</c:v>
+                  <c:v>-795</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1250</c:v>
+                  <c:v>-1060</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1507.5</c:v>
+                  <c:v>-1325</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1682.5</c:v>
+                  <c:v>-1558.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1857.5</c:v>
+                  <c:v>-1770.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-2032.5</c:v>
+                  <c:v>-1982.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2207.5</c:v>
+                  <c:v>-2194.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2382.5</c:v>
+                  <c:v>-2406.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2557.5000000000005</c:v>
+                  <c:v>-2618.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2732.5</c:v>
+                  <c:v>-2830.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="20"/>
@@ -4977,17 +4977,17 @@
         <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -5014,17 +5014,17 @@
         <v>83</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1815.75</v>
       </c>
-      <c r="J8" s="23"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -5114,11 +5114,11 @@
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="23">
+      <c r="I10" s="24">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1722.35</v>
       </c>
-      <c r="J10" s="23"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -5170,13 +5170,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -5484,20 +5484,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
+      <c r="B27" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -5758,17 +5758,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -5776,6 +5765,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -5836,7 +5836,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>75</v>
       </c>
       <c r="C2" s="20"/>
@@ -5876,20 +5876,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6513,20 +6513,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="20"/>
@@ -6640,20 +6640,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7277,20 +7277,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="20"/>
@@ -7407,17 +7407,17 @@
         <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8037,20 +8037,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8120,7 +8120,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="20"/>
@@ -8160,20 +8160,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8793,20 +8793,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>62</v>
       </c>
       <c r="C2" s="20"/>
@@ -8899,8 +8899,8 @@
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
-        <v>86</v>
+      <c r="B3" s="23" t="s">
+        <v>85</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -8937,21 +8937,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -9263,21 +9263,21 @@
         <v>16</v>
       </c>
       <c r="D13" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E13" s="6">
         <f>(D13+F13)/2</f>
-        <v>850</v>
+        <v>1250</v>
       </c>
       <c r="F13" s="3">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="6">
         <f>(F13+H13)/2</f>
-        <v>2350</v>
+        <v>2750</v>
       </c>
       <c r="H13" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="3">
@@ -9306,19 +9306,19 @@
         <v>17</v>
       </c>
       <c r="D14" s="4">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E14" s="4">
-        <v>0.34</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="F14" s="4">
         <v>0.35</v>
       </c>
       <c r="G14" s="4">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="H14" s="4">
         <v>0.36</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0.37</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="4">
@@ -9581,21 +9581,21 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
@@ -9608,17 +9608,17 @@
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
+      <c r="F23" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
@@ -9631,21 +9631,21 @@
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="1">
@@ -9705,154 +9705,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
+      <c r="B34" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -9959,6 +9959,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -9967,17 +9978,6 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10157,47 +10157,47 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>2700</v>
+        <v>2050</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>1971</v>
+        <v>2050</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>1971</v>
+        <v>4050</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>2210</v>
+        <v>2116</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -10244,47 +10244,47 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>3600</v>
+        <v>2950</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>2556</v>
+        <v>2861.5</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>2556</v>
+        <v>4861.5</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>4000</v>
+        <v>3050</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>2600</v>
+        <v>2714.5</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -10331,47 +10331,47 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>3104.9999999999995</v>
+        <v>5619</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>4750</v>
+        <v>3800</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>2945</v>
+        <v>3268</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -10418,47 +10418,47 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>5400</v>
+        <v>4750</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.66999999999999993</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>3617.9999999999995</v>
+        <v>4322.5</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>3617.9999999999995</v>
+        <v>6322.5</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>5500</v>
+        <v>4550</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.22500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.59000000000000008</v>
+        <v>0.83000000000000007</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>3245.0000000000005</v>
+        <v>3776.5000000000005</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -10505,47 +10505,47 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>6300</v>
+        <v>5650</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>4095</v>
+        <v>4972</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>4095</v>
+        <v>6972</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>6250</v>
+        <v>5300</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.56000000000000005</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>3500.0000000000005</v>
+        <v>4240</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -10733,23 +10733,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>135</v>
+        <v>102.5</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>147.5</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>237.5</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>315</v>
+        <v>282.5</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -10774,23 +10774,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>293.23</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>466.45000000000005</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>630</v>
+        <v>551.44000000000005</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -10815,23 +10815,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>405</v>
+        <v>307.5</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>436.30499999999995</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>810</v>
+        <v>682.57500000000005</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>945</v>
+        <v>800.04</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -10856,23 +10856,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>579.38000000000011</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>1080</v>
+        <v>898.7</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>1260</v>
+        <v>1048.6400000000001</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -10897,23 +10897,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>675</v>
+        <v>512.5</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>722.45499999999993</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>1350</v>
+        <v>1114.8249999999998</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>1575</v>
+        <v>1297.2399999999998</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -10938,23 +10938,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>615</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>865.53</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>1620</v>
+        <v>1330.9499999999998</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1890</v>
+        <v>1545.84</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -10979,23 +10979,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>908.55</v>
+        <v>717.49999999999989</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>1207.8</v>
+        <v>1008.6049999999999</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>1505.25</v>
+        <v>1285.1299999999999</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1800.8999999999999</v>
+        <v>1547.0749999999998</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>2094.75</v>
+        <v>1794.4399999999998</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -11020,23 +11020,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>1007.1000000000001</v>
+        <v>920.00000000000011</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>1335.6000000000001</v>
+        <v>1251.68</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>1660.5</v>
+        <v>1566.08</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1981.8000000000002</v>
+        <v>1863.2</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>2299.5</v>
+        <v>2143.04</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -11061,23 +11061,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>1105.6500000000001</v>
+        <v>1122.5</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>1463.4</v>
+        <v>1494.7549999999999</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1815.75</v>
+        <v>1847.03</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>2162.6999999999998</v>
+        <v>2179.3250000000003</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>2504.25</v>
+        <v>2491.64</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -11102,23 +11102,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>1204.2</v>
+        <v>1325</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>1591.2</v>
+        <v>1737.83</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1971</v>
+        <v>2127.98</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>2343.6</v>
+        <v>2495.4499999999998</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>2709</v>
+        <v>2840.24</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -11143,23 +11143,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>1302.75</v>
+        <v>1527.5</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>1719</v>
+        <v>1980.9050000000002</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>2126.25</v>
+        <v>2408.9300000000003</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>2524.5</v>
+        <v>2811.5749999999998</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>2913.75</v>
+        <v>3188.84</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -11184,23 +11184,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>1401.3</v>
+        <v>1730</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>1846.8</v>
+        <v>2223.98</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>2281.5</v>
+        <v>2689.88</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>2705.3999999999996</v>
+        <v>3127.7000000000003</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>3118.5</v>
+        <v>3537.44</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -11225,23 +11225,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>1499.85</v>
+        <v>1932.5000000000005</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1974.6000000000001</v>
+        <v>2467.0550000000003</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>2436.75</v>
+        <v>2970.8300000000004</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>2886.3</v>
+        <v>3443.8250000000003</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>3323.25</v>
+        <v>3886.0400000000004</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -11266,23 +11266,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>1598.4</v>
+        <v>2135</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>2102.3999999999996</v>
+        <v>2710.13</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>2592</v>
+        <v>3251.78</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>3067.2</v>
+        <v>3759.95</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>3528</v>
+        <v>4234.6399999999994</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -11307,23 +11307,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>1696.95</v>
+        <v>2337.5</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>2230.1999999999998</v>
+        <v>2953.2049999999999</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>2747.25</v>
+        <v>3532.73</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>3248.1</v>
+        <v>4076.0750000000003</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>3732.75</v>
+        <v>4583.24</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -11348,23 +11348,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1795.5</v>
+        <v>2540.0000000000005</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>2358</v>
+        <v>3196.28</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>2902.5</v>
+        <v>3813.6800000000003</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>3429</v>
+        <v>4392.2000000000007</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>3937.5</v>
+        <v>4931.8400000000011</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -11389,23 +11389,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1894.0500000000002</v>
+        <v>2742.5</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>2485.8000000000002</v>
+        <v>3439.355</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>3057.75</v>
+        <v>4094.63</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>3609.8999999999996</v>
+        <v>4708.3250000000007</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>4142.25</v>
+        <v>5280.4400000000005</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -11430,23 +11430,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1992.6000000000001</v>
+        <v>2945</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>2613.6000000000004</v>
+        <v>3682.4300000000003</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>3213</v>
+        <v>4375.58</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>3790.8</v>
+        <v>5024.4500000000007</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>4347</v>
+        <v>5629.0400000000009</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -11471,23 +11471,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>2091.1499999999996</v>
+        <v>3147.5</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>2741.3999999999996</v>
+        <v>3925.5050000000001</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>3368.2499999999991</v>
+        <v>4656.5300000000007</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>3971.6999999999994</v>
+        <v>5340.5749999999998</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>4551.75</v>
+        <v>5977.64</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -11512,23 +11512,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>2189.6999999999998</v>
+        <v>3350</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>2869.2</v>
+        <v>4168.58</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>3523.4999999999995</v>
+        <v>4937.4799999999996</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>4152.5999999999995</v>
+        <v>5656.7000000000007</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>4756.5</v>
+        <v>6326.24</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -11847,47 +11847,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>3104.9999999999995</v>
+        <v>4119</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>2210</v>
+        <v>2116</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -11933,47 +11933,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.6</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>3104.9999999999995</v>
+        <v>4869</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>4000</v>
+        <v>3050</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>2600</v>
+        <v>2714.5</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -12019,47 +12019,47 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>3104.9999999999995</v>
+        <v>5619</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>4750</v>
+        <v>3800</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>2945</v>
+        <v>3268</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -12105,47 +12105,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.6</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>3104.9999999999995</v>
+        <v>6369</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>5500</v>
+        <v>4550</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.22500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.59000000000000008</v>
+        <v>0.83000000000000007</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>3245.0000000000005</v>
+        <v>3776.5000000000005</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -12191,47 +12191,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>3104.9999999999995</v>
+        <v>7119</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>6250</v>
+        <v>5300</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.56000000000000005</v>
+        <v>0.8</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>3500.0000000000005</v>
+        <v>4240</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -12413,23 +12413,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -12453,23 +12453,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -12493,23 +12493,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -12533,23 +12533,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -12573,23 +12573,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>1055.25</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -12613,23 +12613,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>1210.5</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>1280.25</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>1350</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>1350</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -12653,23 +12653,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>1365.7499999999998</v>
+        <v>1290.1299999999999</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>1435.5</v>
+        <v>1291.3799999999999</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>1505.25</v>
+        <v>1285.1299999999999</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>1575</v>
+        <v>1285.1299999999999</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>1575</v>
+        <v>1285.1299999999999</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -12693,23 +12693,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>1521</v>
+        <v>1496.08</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>1590.75</v>
+        <v>1534.83</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>1660.5</v>
+        <v>1566.08</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>1730.25</v>
+        <v>1589.83</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>1800</v>
+        <v>1606.08</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -12733,23 +12733,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1676.25</v>
+        <v>1702.03</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1746</v>
+        <v>1778.28</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1815.75</v>
+        <v>1847.03</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1885.5</v>
+        <v>1908.28</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1955.25</v>
+        <v>1962.0300000000002</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -12773,23 +12773,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1831.4999999999998</v>
+        <v>1907.98</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1901.25</v>
+        <v>2021.73</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1971</v>
+        <v>2127.98</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>2040.75</v>
+        <v>2226.73</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>2110.5</v>
+        <v>2317.98</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -12813,23 +12813,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1986.75</v>
+        <v>2113.9300000000003</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>2056.5</v>
+        <v>2265.1800000000003</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>2126.25</v>
+        <v>2408.9300000000003</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>2196</v>
+        <v>2545.1800000000003</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>2265.75</v>
+        <v>2673.9300000000003</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -12853,23 +12853,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>2142</v>
+        <v>2319.88</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>2211.75</v>
+        <v>2508.63</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>2281.5</v>
+        <v>2689.88</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>2351.25</v>
+        <v>2863.63</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>2421</v>
+        <v>3029.88</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -12893,23 +12893,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>2297.25</v>
+        <v>2525.8300000000004</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>2367</v>
+        <v>2752.0800000000004</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>2436.75</v>
+        <v>2970.8300000000004</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>2506.5</v>
+        <v>3182.0800000000004</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>2576.25</v>
+        <v>3385.8300000000004</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -12933,23 +12933,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>2452.4999999999995</v>
+        <v>2731.78</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>2522.2499999999995</v>
+        <v>2995.53</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>2592</v>
+        <v>3251.78</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>2661.75</v>
+        <v>3500.53</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>2731.4999999999995</v>
+        <v>3741.78</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -12973,23 +12973,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>2607.75</v>
+        <v>2937.73</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>2677.5</v>
+        <v>3238.98</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>2747.25</v>
+        <v>3532.73</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>2817</v>
+        <v>3818.98</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>2886.75</v>
+        <v>4097.7299999999996</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -13013,23 +13013,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>2763</v>
+        <v>3143.6800000000003</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>2832.75</v>
+        <v>3482.4300000000003</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>2902.5</v>
+        <v>3813.6800000000003</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>2972.25</v>
+        <v>4137.43</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>3042</v>
+        <v>4453.68</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -13053,23 +13053,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>2918.2499999999991</v>
+        <v>3349.63</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>2987.9999999999995</v>
+        <v>3725.88</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>3057.75</v>
+        <v>4094.63</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>3127.5</v>
+        <v>4455.88</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>3197.2499999999995</v>
+        <v>4809.63</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -13093,23 +13093,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>3073.4999999999995</v>
+        <v>3555.5800000000004</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>3143.25</v>
+        <v>3969.3300000000004</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>3213</v>
+        <v>4375.58</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>3282.75</v>
+        <v>4774.33</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>3352.5</v>
+        <v>5165.5800000000008</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -13133,23 +13133,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>3228.7499999999995</v>
+        <v>3761.53</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>3298.4999999999995</v>
+        <v>4212.7800000000007</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>3368.2499999999991</v>
+        <v>4656.5300000000007</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>3437.9999999999995</v>
+        <v>5092.7800000000007</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>3507.7499999999995</v>
+        <v>5521.5300000000007</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -13173,23 +13173,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>3384</v>
+        <v>3967.48</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>3453.7499999999995</v>
+        <v>4456.2299999999996</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>3523.4999999999995</v>
+        <v>4937.4799999999996</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>3593.25</v>
+        <v>5411.23</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>3662.9999999999995</v>
+        <v>5877.48</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -15153,47 +15153,47 @@
       </c>
       <c r="F125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>2700</v>
+        <v>2050</v>
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="I125" s="8">
         <f>F125*H125</f>
-        <v>1971</v>
+        <v>2050</v>
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>1971</v>
+        <v>2550</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>3250</v>
+        <v>2300</v>
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="O125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>2210</v>
+        <v>2116</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -15239,47 +15239,47 @@
       </c>
       <c r="F126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>3600</v>
+        <v>2950</v>
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="I126" s="8">
         <f>F126*H126</f>
-        <v>2556</v>
+        <v>2861.5</v>
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
-        <v>0.6</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>2556</v>
+        <v>4111.5</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>4000</v>
+        <v>3050</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="O126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>2600</v>
+        <v>2714.5</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -15325,47 +15325,47 @@
       </c>
       <c r="F127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>4500</v>
+        <v>3850</v>
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I127" s="8">
         <f>F127*H127</f>
-        <v>3104.9999999999995</v>
+        <v>3619</v>
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>3104.9999999999995</v>
+        <v>5619</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>4750</v>
+        <v>3800</v>
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>2945</v>
+        <v>3268</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -15411,47 +15411,47 @@
       </c>
       <c r="F128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>5400</v>
+        <v>4750</v>
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="H128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
-        <v>0.66999999999999993</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="I128" s="8">
         <f>F128*H128</f>
-        <v>3617.9999999999995</v>
+        <v>4322.5</v>
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
-        <v>0.6</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>3617.9999999999995</v>
+        <v>7072.5</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>5500</v>
+        <v>4550</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.22500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
-        <v>0.59000000000000008</v>
+        <v>0.83000000000000007</v>
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>3245.0000000000005</v>
+        <v>3776.5000000000005</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -15497,47 +15497,47 @@
       </c>
       <c r="F129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>6300</v>
+        <v>5650</v>
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="H129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="I129" s="8">
         <f>F129*H129</f>
-        <v>4095</v>
+        <v>4972</v>
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>4095</v>
+        <v>8472</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>6250</v>
+        <v>5300</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="O129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
-        <v>0.56000000000000005</v>
+        <v>0.8</v>
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>3500.0000000000005</v>
+        <v>4240</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -15749,43 +15749,43 @@
       </c>
       <c r="C135" s="15">
         <f t="shared" si="15"/>
-        <v>135</v>
+        <v>102.5</v>
       </c>
       <c r="D135" s="15">
         <f t="shared" si="16"/>
-        <v>180</v>
+        <v>147.5</v>
       </c>
       <c r="E135" s="15">
         <f t="shared" si="17"/>
-        <v>225</v>
+        <v>192.5</v>
       </c>
       <c r="F135" s="15">
         <f t="shared" si="18"/>
-        <v>270</v>
+        <v>237.5</v>
       </c>
       <c r="G135" s="15">
         <f t="shared" si="19"/>
-        <v>315</v>
+        <v>282.5</v>
       </c>
       <c r="H135" s="15">
         <f t="shared" si="20"/>
-        <v>-162.5</v>
+        <v>-115</v>
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-200</v>
+        <v>-152.5</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
-        <v>-237.5</v>
+        <v>-190</v>
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-275</v>
+        <v>-227.5</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-312.5</v>
+        <v>-265</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -15804,43 +15804,43 @@
       </c>
       <c r="C136" s="15">
         <f t="shared" si="15"/>
-        <v>270</v>
+        <v>205</v>
       </c>
       <c r="D136" s="15">
         <f t="shared" si="16"/>
-        <v>360</v>
+        <v>293.23</v>
       </c>
       <c r="E136" s="15">
         <f t="shared" si="17"/>
-        <v>450</v>
+        <v>380.38</v>
       </c>
       <c r="F136" s="15">
         <f t="shared" si="18"/>
-        <v>540</v>
+        <v>466.45000000000005</v>
       </c>
       <c r="G136" s="15">
         <f t="shared" si="19"/>
-        <v>630</v>
+        <v>551.44000000000005</v>
       </c>
       <c r="H136" s="15">
         <f t="shared" si="20"/>
-        <v>-325</v>
+        <v>-230</v>
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-400</v>
+        <v>-305</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
-        <v>-475</v>
+        <v>-380</v>
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-550</v>
+        <v>-455</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-625</v>
+        <v>-530</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -15859,43 +15859,43 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>405</v>
+        <v>307.5</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>540</v>
+        <v>436.30499999999995</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>675</v>
+        <v>561.32999999999993</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>810</v>
+        <v>682.57500000000005</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>945</v>
+        <v>800.04</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
-        <v>-487.5</v>
+        <v>-345</v>
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-600</v>
+        <v>-457.5</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
-        <v>-712.5</v>
+        <v>-570</v>
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-825</v>
+        <v>-682.5</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-937.5</v>
+        <v>-795</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -15914,43 +15914,43 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>720</v>
+        <v>579.38000000000011</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>900</v>
+        <v>742.28</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>1080</v>
+        <v>898.7</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>1260</v>
+        <v>1048.6400000000001</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
-        <v>-650</v>
+        <v>-460</v>
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-800</v>
+        <v>-610</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
-        <v>-950</v>
+        <v>-760</v>
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-1100</v>
+        <v>-910</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-1250</v>
+        <v>-1060</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -15969,43 +15969,43 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>638.54999999999995</v>
+        <v>512.5</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>900</v>
+        <v>722.45499999999993</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>1125</v>
+        <v>923.2299999999999</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>1350</v>
+        <v>1114.8249999999998</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>1575</v>
+        <v>1297.2399999999998</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-770.9</v>
+        <v>-571.31999999999994</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-951</v>
+        <v>-759.14499999999998</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
-        <v>-1133.3499999999999</v>
+        <v>-950</v>
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-1318.625</v>
+        <v>-1137.5</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-1507.5</v>
+        <v>-1325</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -16024,43 +16024,43 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>737.09999999999991</v>
+        <v>615</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>1027.8</v>
+        <v>865.53</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>1350</v>
+        <v>1104.1799999999998</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>1620</v>
+        <v>1330.9499999999998</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1890</v>
+        <v>1545.84</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-881.4</v>
+        <v>-677.11999999999989</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-1081</v>
+        <v>-894.87</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-1280.5999999999999</v>
+        <v>-1113.4000000000001</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-1480.875</v>
+        <v>-1334.06</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-1682.5</v>
+        <v>-1558.1999999999998</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -16079,43 +16079,43 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>835.64999999999986</v>
+        <v>722.49999999999989</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>1155.5999999999999</v>
+        <v>1014.8549999999999</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>1505.25</v>
+        <v>1285.1299999999999</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1889.9999999999998</v>
+        <v>1547.0749999999998</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>2205</v>
+        <v>1794.4399999999998</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-991.9</v>
+        <v>-782.92</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-1211</v>
+        <v>-1030.595</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-1427.85</v>
+        <v>-1276.8</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-1643.125</v>
+        <v>-1522.885</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1857.5</v>
+        <v>-1770.1999999999998</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -16134,43 +16134,43 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>934.2</v>
+        <v>850</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>1283.4000000000001</v>
+        <v>1220.43</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>1660.5</v>
+        <v>1566.08</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>2070.9</v>
+        <v>1886.9500000000003</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>2520</v>
+        <v>2183.04</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-1102.4000000000001</v>
+        <v>-888.72</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-1341</v>
+        <v>-1166.3200000000002</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-1575.1</v>
+        <v>-1440.2</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-1805.375</v>
+        <v>-1711.71</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-2032.5</v>
+        <v>-1982.2</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -16189,43 +16189,43 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>1032.75</v>
+        <v>977.5</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>1411.2</v>
+        <v>1426.0049999999999</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>1815.75</v>
+        <v>1847.03</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>2251.7999999999997</v>
+        <v>2240.5750000000003</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>2724.75</v>
+        <v>2606.64</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-1212.9000000000001</v>
+        <v>-994.52</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-1471</v>
+        <v>-1302.0450000000001</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-1722.35</v>
+        <v>-1603.6</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1967.625</v>
+        <v>-1900.5350000000001</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-2207.5</v>
+        <v>-2194.1999999999998</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -16244,43 +16244,43 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>1131.3</v>
+        <v>1105</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>1539</v>
+        <v>1631.58</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>1971</v>
+        <v>2127.98</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>2432.6999999999998</v>
+        <v>2594.1999999999998</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>2929.5</v>
+        <v>3030.24</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-1323.4</v>
+        <v>-1100.3200000000002</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-1601</v>
+        <v>-1437.77</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-1869.6</v>
+        <v>-1767</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-2129.875</v>
+        <v>-2089.36</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-2382.5</v>
+        <v>-2406.1999999999998</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -16299,43 +16299,43 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>1229.8499999999999</v>
+        <v>1232.5</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>1666.8000000000002</v>
+        <v>1837.1550000000002</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>2126.25</v>
+        <v>2408.9300000000003</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>2613.6</v>
+        <v>2947.8249999999998</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>3134.25</v>
+        <v>3453.84</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-1433.9</v>
+        <v>-1206.1200000000001</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-1731.0000000000002</v>
+        <v>-1573.4950000000001</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-2016.8500000000004</v>
+        <v>-1930.4</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-2292.1250000000005</v>
+        <v>-2278.1850000000004</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-2557.5000000000005</v>
+        <v>-2618.1999999999998</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -16354,43 +16354,43 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>1328.4</v>
+        <v>1360</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>1794.6</v>
+        <v>2042.73</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>2281.5</v>
+        <v>2689.88</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>2794.4999999999995</v>
+        <v>3301.4500000000003</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>3339</v>
+        <v>3877.44</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-1544.4</v>
+        <v>-1311.92</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-1861</v>
+        <v>-1709.2199999999998</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-2164.1</v>
+        <v>-2093.8000000000002</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-2454.375</v>
+        <v>-2467.0100000000002</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-2732.5</v>
+        <v>-2830.2</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -16409,43 +16409,43 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>1426.95</v>
+        <v>1487.5000000000002</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1922.4</v>
+        <v>2248.3050000000003</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>2436.75</v>
+        <v>2970.8300000000004</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>2975.3999999999996</v>
+        <v>3655.0750000000003</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>3543.75</v>
+        <v>4301.0400000000009</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-1654.9</v>
+        <v>-1417.7200000000003</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-1991.0000000000002</v>
+        <v>-1844.9450000000002</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-2311.3500000000004</v>
+        <v>-2257.1999999999998</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-2616.625</v>
+        <v>-2655.835</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-2907.5</v>
+        <v>-3042.2</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -16464,43 +16464,43 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>1525.5</v>
+        <v>1615</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>2050.1999999999998</v>
+        <v>2453.88</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>2592</v>
+        <v>3251.78</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>3156.2999999999993</v>
+        <v>4008.7</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>3748.5</v>
+        <v>4724.6399999999994</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-1765.4</v>
+        <v>-1523.52</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-2121</v>
+        <v>-1980.6699999999998</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-2458.6</v>
+        <v>-2420.6</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-2778.875</v>
+        <v>-2844.66</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-3082.5</v>
+        <v>-3254.2</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -16519,43 +16519,43 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>1624.0500000000002</v>
+        <v>1742.5</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>2178</v>
+        <v>2659.4549999999999</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>2747.25</v>
+        <v>3532.73</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>3337.2</v>
+        <v>4362.3250000000007</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>3953.25</v>
+        <v>5148.24</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-1875.9</v>
+        <v>-1629.32</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-2251</v>
+        <v>-2116.395</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-2605.8500000000004</v>
+        <v>-2584</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-2941.125</v>
+        <v>-3033.4850000000001</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-3257.5</v>
+        <v>-3466.2</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -16574,43 +16574,43 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>1722.6000000000001</v>
+        <v>1870.0000000000002</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>2305.8000000000002</v>
+        <v>2865.03</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>2902.5</v>
+        <v>3813.6800000000003</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>3518.1</v>
+        <v>4715.9500000000007</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>4158</v>
+        <v>5571.8400000000011</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-1986.4</v>
+        <v>-1735.1200000000001</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-2381</v>
+        <v>-2252.12</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-2753.1000000000004</v>
+        <v>-2747.4</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-3103.3750000000005</v>
+        <v>-3222.3100000000004</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-3432.5000000000005</v>
+        <v>-3678.2000000000003</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -16629,43 +16629,43 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>1821.1499999999999</v>
+        <v>1997.5</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>2433.6</v>
+        <v>3070.605</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>3057.75</v>
+        <v>4094.63</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>3698.9999999999995</v>
+        <v>5069.5750000000007</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>4362.75</v>
+        <v>5995.4400000000005</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-2096.9</v>
+        <v>-1840.92</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-2511</v>
+        <v>-2387.8450000000003</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-2900.35</v>
+        <v>-2910.8</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-3265.625</v>
+        <v>-3411.1350000000002</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-3607.5000000000005</v>
+        <v>-3890.2</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -16684,43 +16684,43 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1919.6999999999998</v>
+        <v>2125</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>2561.4</v>
+        <v>3276.1800000000003</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>3213</v>
+        <v>4375.58</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>3879.8999999999996</v>
+        <v>5423.2000000000007</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>4567.5</v>
+        <v>6419.0400000000009</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-2207.4</v>
+        <v>-1946.72</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-2641</v>
+        <v>-2523.5700000000002</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-3047.6000000000004</v>
+        <v>-3074.2000000000003</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-3427.8750000000005</v>
+        <v>-3599.9600000000005</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-3782.5000000000005</v>
+        <v>-4102.2</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -16739,43 +16739,43 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>2018.25</v>
+        <v>2252.5</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>2689.2</v>
+        <v>3481.7550000000001</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>3368.2499999999991</v>
+        <v>4656.5300000000007</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>4060.7999999999993</v>
+        <v>5776.8249999999998</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>4772.25</v>
+        <v>6842.64</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-2317.9</v>
+        <v>-2052.52</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-2771</v>
+        <v>-2659.2950000000001</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-3194.85</v>
+        <v>-3237.6</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-3590.1250000000005</v>
+        <v>-3788.7850000000003</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-3957.5000000000005</v>
+        <v>-4314.2</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -16794,43 +16794,43 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>2116.8000000000002</v>
+        <v>2380</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>2817</v>
+        <v>3687.33</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>3523.4999999999995</v>
+        <v>4937.4799999999996</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>4241.7</v>
+        <v>6130.4500000000007</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>4977</v>
+        <v>7266.24</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-2428.4</v>
+        <v>-2158.3199999999997</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-2901</v>
+        <v>-2795.02</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-3342.1</v>
+        <v>-3401</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-3752.3750000000005</v>
+        <v>-3977.61</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-4132.5</v>
+        <v>-4526.2</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>

--- a/docs/damping_curve_MRAx0.xlsx
+++ b/docs/damping_curve_MRAx0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E35C9C-723E-4F64-BADA-4A948CDE19C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CA6CC-DDCF-4DFA-8B8D-8D400F134D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -491,23 +491,20 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -515,8 +512,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -666,40 +666,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>102.5</c:v>
+                  <c:v>92.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>205</c:v>
+                  <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>307.5</c:v>
+                  <c:v>277.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>410</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>512.5</c:v>
+                  <c:v>462.49999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>615</c:v>
+                  <c:v>555</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>717.49999999999989</c:v>
+                  <c:v>647.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>920.00000000000011</c:v>
+                  <c:v>827.50000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1122.5</c:v>
+                  <c:v>1007.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1325</c:v>
+                  <c:v>1187.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1527.5</c:v>
+                  <c:v>1367.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1730</c:v>
+                  <c:v>1547.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,40 +794,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>147.5</c:v>
+                  <c:v>137.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>293.23</c:v>
+                  <c:v>273.35000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>436.30499999999995</c:v>
+                  <c:v>406.72500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>579.38000000000011</c:v>
+                  <c:v>540.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>722.45499999999993</c:v>
+                  <c:v>673.47499999999991</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>865.53</c:v>
+                  <c:v>806.84999999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1008.6049999999999</c:v>
+                  <c:v>940.22499999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1251.68</c:v>
+                  <c:v>1161.0999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1494.7549999999999</c:v>
+                  <c:v>1381.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1737.83</c:v>
+                  <c:v>1602.85</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1980.9050000000002</c:v>
+                  <c:v>1823.7250000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2223.98</c:v>
+                  <c:v>2044.6000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -922,40 +922,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1285.1299999999999</c:v>
+                  <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1566.08</c:v>
+                  <c:v>1477.42</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1847.03</c:v>
+                  <c:v>1736.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2127.98</c:v>
+                  <c:v>1995.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2408.9300000000003</c:v>
+                  <c:v>2254.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2689.88</c:v>
+                  <c:v>2513.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1050,40 +1050,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>237.5</c:v>
+                  <c:v>227.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>466.45000000000005</c:v>
+                  <c:v>446.81</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>682.57500000000005</c:v>
+                  <c:v>653.83500000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>898.7</c:v>
+                  <c:v>860.86</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1114.8249999999998</c:v>
+                  <c:v>1067.885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1330.9499999999998</c:v>
+                  <c:v>1274.9099999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1547.0749999999998</c:v>
+                  <c:v>1481.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1863.2</c:v>
+                  <c:v>1776.46</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2179.3250000000003</c:v>
+                  <c:v>2070.9850000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2495.4499999999998</c:v>
+                  <c:v>2365.5100000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2811.5749999999998</c:v>
+                  <c:v>2660.0349999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3127.7000000000003</c:v>
+                  <c:v>2954.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,40 +1178,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>282.5</c:v>
+                  <c:v>272.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>551.44000000000005</c:v>
+                  <c:v>531.92000000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>800.04</c:v>
+                  <c:v>771.72</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1048.6400000000001</c:v>
+                  <c:v>1011.5200000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1297.2399999999998</c:v>
+                  <c:v>1251.32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1545.84</c:v>
+                  <c:v>1491.12</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1794.4399999999998</c:v>
+                  <c:v>1730.9199999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2143.04</c:v>
+                  <c:v>2058.2200000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2491.64</c:v>
+                  <c:v>2385.52</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2840.24</c:v>
+                  <c:v>2712.8199999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3188.84</c:v>
+                  <c:v>3040.1200000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3537.44</c:v>
+                  <c:v>3367.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1506,40 +1506,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1290.1299999999999</c:v>
+                  <c:v>1220.8699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1496.08</c:v>
+                  <c:v>1404.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1702.03</c:v>
+                  <c:v>1588.97</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1907.98</c:v>
+                  <c:v>1773.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2113.9300000000003</c:v>
+                  <c:v>1957.0700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2319.88</c:v>
+                  <c:v>2141.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1634,40 +1634,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1291.3799999999999</c:v>
+                  <c:v>1223.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1534.83</c:v>
+                  <c:v>1444.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1778.28</c:v>
+                  <c:v>1666.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2021.73</c:v>
+                  <c:v>1888.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2265.1800000000003</c:v>
+                  <c:v>2109.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2508.63</c:v>
+                  <c:v>2331.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,40 +1762,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1285.1299999999999</c:v>
+                  <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1566.08</c:v>
+                  <c:v>1477.42</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1847.03</c:v>
+                  <c:v>1736.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2127.98</c:v>
+                  <c:v>1995.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2408.9300000000003</c:v>
+                  <c:v>2254.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2689.88</c:v>
+                  <c:v>2513.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1890,40 +1890,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1285.1299999999999</c:v>
+                  <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1589.83</c:v>
+                  <c:v>1502.42</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1908.28</c:v>
+                  <c:v>1798.97</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2226.73</c:v>
+                  <c:v>2095.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2545.1800000000003</c:v>
+                  <c:v>2392.0700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2863.63</c:v>
+                  <c:v>2688.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,40 +2018,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1285.1299999999999</c:v>
+                  <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1606.08</c:v>
+                  <c:v>1519.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1962.0300000000002</c:v>
+                  <c:v>1853.97</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2317.98</c:v>
+                  <c:v>2188.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2673.9300000000003</c:v>
+                  <c:v>2522.0700000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3029.88</c:v>
+                  <c:v>2856.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,40 +2346,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>487.5</c:v>
+                  <c:v>315</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>650</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>770.9</c:v>
+                  <c:v>521.64</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>881.4</c:v>
+                  <c:v>618.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>991.9</c:v>
+                  <c:v>714.83999999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1102.4000000000001</c:v>
+                  <c:v>811.44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1212.9000000000001</c:v>
+                  <c:v>908.04</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1323.4</c:v>
+                  <c:v>1004.64</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1433.9</c:v>
+                  <c:v>1101.2400000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1544.4</c:v>
+                  <c:v>1197.8400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2474,40 +2474,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>142.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>285</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>600</c:v>
+                  <c:v>427.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>800</c:v>
+                  <c:v>570</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>951</c:v>
+                  <c:v>709.36500000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1081</c:v>
+                  <c:v>836.19</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1211</c:v>
+                  <c:v>963.01499999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1341</c:v>
+                  <c:v>1089.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1471</c:v>
+                  <c:v>1216.665</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1601</c:v>
+                  <c:v>1343.49</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1731.0000000000002</c:v>
+                  <c:v>1470.3150000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1861</c:v>
+                  <c:v>1597.1399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2602,40 +2602,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>237.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>475</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>712.5</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>950</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1133.3499999999999</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1280.5999999999999</c:v>
+                  <c:v>1054.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1427.85</c:v>
+                  <c:v>1209.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1575.1</c:v>
+                  <c:v>1364.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1722.35</c:v>
+                  <c:v>1519.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1869.6</c:v>
+                  <c:v>1674</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2016.8500000000004</c:v>
+                  <c:v>1828.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2164.1</c:v>
+                  <c:v>1983.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2730,40 +2730,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275</c:v>
+                  <c:v>217.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>550</c:v>
+                  <c:v>435</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>825</c:v>
+                  <c:v>652.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1100</c:v>
+                  <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1318.625</c:v>
+                  <c:v>1087.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1480.875</c:v>
+                  <c:v>1275.42</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1643.125</c:v>
+                  <c:v>1455.9449999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1805.375</c:v>
+                  <c:v>1636.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1967.625</c:v>
+                  <c:v>1816.9950000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2129.875</c:v>
+                  <c:v>1997.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2292.1250000000005</c:v>
+                  <c:v>2178.0450000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2454.375</c:v>
+                  <c:v>2358.5699999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2858,40 +2858,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>312.5</c:v>
+                  <c:v>255</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>625</c:v>
+                  <c:v>510</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>937.5</c:v>
+                  <c:v>765</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1250</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1507.5</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1682.5</c:v>
+                  <c:v>1499.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1857.5</c:v>
+                  <c:v>1703.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2032.5</c:v>
+                  <c:v>1907.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2207.5</c:v>
+                  <c:v>2111.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2382.5</c:v>
+                  <c:v>2315.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2557.5000000000005</c:v>
+                  <c:v>2519.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2732.5</c:v>
+                  <c:v>2723.3999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3179,40 +3179,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>102.5</c:v>
+                  <c:v>92.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>205</c:v>
+                  <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>307.5</c:v>
+                  <c:v>277.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>410</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>512.5</c:v>
+                  <c:v>462.49999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>615</c:v>
+                  <c:v>555</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>722.49999999999989</c:v>
+                  <c:v>650</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>850</c:v>
+                  <c:v>755</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>977.5</c:v>
+                  <c:v>860</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1105</c:v>
+                  <c:v>965</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1232.5</c:v>
+                  <c:v>1070</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1360</c:v>
+                  <c:v>1175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3307,40 +3307,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>147.5</c:v>
+                  <c:v>137.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>293.23</c:v>
+                  <c:v>273.35000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>436.30499999999995</c:v>
+                  <c:v>406.72500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>579.38000000000011</c:v>
+                  <c:v>540.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>722.45499999999993</c:v>
+                  <c:v>673.47499999999991</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>865.53</c:v>
+                  <c:v>806.84999999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1014.8549999999999</c:v>
+                  <c:v>945.22499999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1220.43</c:v>
+                  <c:v>1128.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1426.0049999999999</c:v>
+                  <c:v>1311.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1631.58</c:v>
+                  <c:v>1495.35</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1837.1550000000002</c:v>
+                  <c:v>1678.7250000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2042.73</c:v>
+                  <c:v>1862.1000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3435,40 +3435,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.5</c:v>
+                  <c:v>182.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.38</c:v>
+                  <c:v>360.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561.32999999999993</c:v>
+                  <c:v>532.16999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>742.28</c:v>
+                  <c:v>703.72</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>923.2299999999999</c:v>
+                  <c:v>875.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1104.1799999999998</c:v>
+                  <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1285.1299999999999</c:v>
+                  <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1566.08</c:v>
+                  <c:v>1477.42</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1847.03</c:v>
+                  <c:v>1736.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2127.98</c:v>
+                  <c:v>1995.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2408.9300000000003</c:v>
+                  <c:v>2254.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2689.88</c:v>
+                  <c:v>2513.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3563,40 +3563,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>237.5</c:v>
+                  <c:v>227.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>466.45000000000005</c:v>
+                  <c:v>446.81</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>682.57500000000005</c:v>
+                  <c:v>653.83500000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>898.7</c:v>
+                  <c:v>860.86</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1114.8249999999998</c:v>
+                  <c:v>1067.885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1330.9499999999998</c:v>
+                  <c:v>1274.9099999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1547.0749999999998</c:v>
+                  <c:v>1481.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1886.9500000000003</c:v>
+                  <c:v>1801.46</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2240.5750000000003</c:v>
+                  <c:v>2133.4850000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2594.1999999999998</c:v>
+                  <c:v>2465.5100000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2947.8249999999998</c:v>
+                  <c:v>2797.5349999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3301.4500000000003</c:v>
+                  <c:v>3129.56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3691,40 +3691,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>282.5</c:v>
+                  <c:v>272.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>551.44000000000005</c:v>
+                  <c:v>531.92000000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>800.04</c:v>
+                  <c:v>771.72</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1048.6400000000001</c:v>
+                  <c:v>1011.5200000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1297.2399999999998</c:v>
+                  <c:v>1251.32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1545.84</c:v>
+                  <c:v>1491.12</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1794.4399999999998</c:v>
+                  <c:v>1730.9199999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2183.04</c:v>
+                  <c:v>2100.7200000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2606.64</c:v>
+                  <c:v>2503.02</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3030.24</c:v>
+                  <c:v>2905.3199999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3453.84</c:v>
+                  <c:v>3307.6200000000008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3877.44</c:v>
+                  <c:v>3709.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3819,40 +3819,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-115</c:v>
+                  <c:v>-105</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-230</c:v>
+                  <c:v>-210</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-345</c:v>
+                  <c:v>-315</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-460</c:v>
+                  <c:v>-420</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-571.31999999999994</c:v>
+                  <c:v>-521.64</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-677.11999999999989</c:v>
+                  <c:v>-618.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-782.92</c:v>
+                  <c:v>-714.83999999999992</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-888.72</c:v>
+                  <c:v>-811.44</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-994.52</c:v>
+                  <c:v>-908.04</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1100.3200000000002</c:v>
+                  <c:v>-1004.64</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1206.1200000000001</c:v>
+                  <c:v>-1101.2400000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1311.92</c:v>
+                  <c:v>-1197.8400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3947,40 +3947,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-152.5</c:v>
+                  <c:v>-142.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-305</c:v>
+                  <c:v>-285</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-457.5</c:v>
+                  <c:v>-427.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-610</c:v>
+                  <c:v>-570</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-759.14499999999998</c:v>
+                  <c:v>-709.36500000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-894.87</c:v>
+                  <c:v>-836.19</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1030.595</c:v>
+                  <c:v>-963.01499999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1166.3200000000002</c:v>
+                  <c:v>-1089.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1302.0450000000001</c:v>
+                  <c:v>-1216.665</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1437.77</c:v>
+                  <c:v>-1343.49</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1573.4950000000001</c:v>
+                  <c:v>-1470.3150000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1709.2199999999998</c:v>
+                  <c:v>-1597.1399999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4075,40 +4075,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-190</c:v>
+                  <c:v>-180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-380</c:v>
+                  <c:v>-360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-570</c:v>
+                  <c:v>-540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-760</c:v>
+                  <c:v>-720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-950</c:v>
+                  <c:v>-900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1113.4000000000001</c:v>
+                  <c:v>-1054.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1276.8</c:v>
+                  <c:v>-1209.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1440.2</c:v>
+                  <c:v>-1364.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1603.6</c:v>
+                  <c:v>-1519.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1767</c:v>
+                  <c:v>-1674</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1930.4</c:v>
+                  <c:v>-1828.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2093.8000000000002</c:v>
+                  <c:v>-1983.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4203,40 +4203,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-227.5</c:v>
+                  <c:v>-217.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-455</c:v>
+                  <c:v>-435</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-682.5</c:v>
+                  <c:v>-652.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-910</c:v>
+                  <c:v>-870</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1137.5</c:v>
+                  <c:v>-1087.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1334.06</c:v>
+                  <c:v>-1275.42</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1522.885</c:v>
+                  <c:v>-1455.9449999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1711.71</c:v>
+                  <c:v>-1636.47</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1900.5350000000001</c:v>
+                  <c:v>-1816.9950000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2089.36</c:v>
+                  <c:v>-1997.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2278.1850000000004</c:v>
+                  <c:v>-2178.0450000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2467.0100000000002</c:v>
+                  <c:v>-2358.5699999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4331,40 +4331,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-265</c:v>
+                  <c:v>-255</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-530</c:v>
+                  <c:v>-510</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-795</c:v>
+                  <c:v>-765</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1060</c:v>
+                  <c:v>-1020</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-1325</c:v>
+                  <c:v>-1275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1558.1999999999998</c:v>
+                  <c:v>-1499.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1770.1999999999998</c:v>
+                  <c:v>-1703.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1982.2</c:v>
+                  <c:v>-1907.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-2194.1999999999998</c:v>
+                  <c:v>-2111.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-2406.1999999999998</c:v>
+                  <c:v>-2315.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2618.1999999999998</c:v>
+                  <c:v>-2519.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2830.2</c:v>
+                  <c:v>-2723.3999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="20"/>
@@ -4974,20 +4974,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -5018,13 +5018,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
-      <c r="I8" s="24">
+      <c r="I8" s="26">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>1815.75</v>
-      </c>
-      <c r="J8" s="24"/>
+        <v>1736.47</v>
+      </c>
+      <c r="J8" s="26"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -5114,11 +5114,11 @@
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="24">
+      <c r="I10" s="26">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1722.35</v>
-      </c>
-      <c r="J10" s="24"/>
+        <v>1519.2</v>
+      </c>
+      <c r="J10" s="26"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -5170,13 +5170,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -5201,7 +5201,7 @@
       <c r="H14" s="20"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
-        <v>4500</v>
+        <v>3650</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>16</v>
@@ -5230,7 +5230,7 @@
       <c r="H15" s="20"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
-        <v>3104.9999999999995</v>
+        <v>3431</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>16</v>
@@ -5254,7 +5254,7 @@
       <c r="H16" s="20"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>16</v>
@@ -5278,7 +5278,7 @@
       <c r="H17" s="20"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
-        <v>3104.9999999999995</v>
+        <v>5181</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>16</v>
@@ -5324,7 +5324,7 @@
       <c r="H19" s="20"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
-        <v>4750</v>
+        <v>3600</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>16</v>
@@ -5348,7 +5348,7 @@
       <c r="H20" s="20"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
-        <v>2945</v>
+        <v>3096</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>16</v>
@@ -5389,7 +5389,7 @@
       <c r="H22" s="20"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>17</v>
@@ -5413,7 +5413,7 @@
       <c r="H23" s="20"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>17</v>
@@ -5437,7 +5437,7 @@
       <c r="H24" s="20"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>17</v>
@@ -5484,20 +5484,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -5758,6 +5758,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -5765,17 +5776,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -5836,7 +5836,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>75</v>
       </c>
       <c r="C2" s="20"/>
@@ -5879,17 +5879,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6513,20 +6513,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="20"/>
@@ -6643,17 +6643,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7277,20 +7277,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="20"/>
@@ -7404,20 +7404,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8037,20 +8037,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8120,7 +8120,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="20"/>
@@ -8163,17 +8163,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8793,20 +8793,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>62</v>
       </c>
       <c r="C2" s="20"/>
@@ -8899,7 +8899,7 @@
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>85</v>
       </c>
       <c r="C3" s="20"/>
@@ -8937,21 +8937,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -9128,39 +9128,39 @@
         <v>16</v>
       </c>
       <c r="D10" s="3">
-        <v>2050</v>
+        <v>1850</v>
       </c>
       <c r="E10" s="6">
         <f>(D10+F10)/2</f>
-        <v>2950</v>
+        <v>2750</v>
       </c>
       <c r="F10" s="3">
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G10" s="6">
         <f>(F10+H10)/2</f>
-        <v>4750</v>
+        <v>4550</v>
       </c>
       <c r="H10" s="3">
-        <v>5650</v>
+        <v>5450</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="3">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="K10" s="6">
         <f>(J10+L10)/2</f>
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="L10" s="3">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="M10" s="6">
         <f>(L10+N10)/2</f>
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="N10" s="3">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="O10" s="1"/>
     </row>
@@ -9263,21 +9263,21 @@
         <v>16</v>
       </c>
       <c r="D13" s="3">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E13" s="6">
         <f>(D13+F13)/2</f>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="3">
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="G13" s="6">
         <f>(F13+H13)/2</f>
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="H13" s="3">
-        <v>3500</v>
+        <v>3250</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="3">
@@ -9419,39 +9419,39 @@
         <v>16</v>
       </c>
       <c r="D17" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="E17" s="6">
         <f>(D17+F17)/2</f>
-        <v>3050</v>
+        <v>2850</v>
       </c>
       <c r="F17" s="3">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="G17" s="6">
         <f>(F17+H17)/2</f>
-        <v>4550</v>
+        <v>4350</v>
       </c>
       <c r="H17" s="3">
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="3">
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="K17" s="6">
         <f>(J17+L17)/2</f>
-        <v>4000</v>
+        <v>3750</v>
       </c>
       <c r="L17" s="3">
-        <v>4750</v>
+        <v>4500</v>
       </c>
       <c r="M17" s="6">
         <f>(L17+N17)/2</f>
-        <v>5500</v>
+        <v>5250</v>
       </c>
       <c r="N17" s="3">
-        <v>6250</v>
+        <v>6000</v>
       </c>
       <c r="O17" s="1"/>
     </row>
@@ -9581,21 +9581,21 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
@@ -9608,17 +9608,17 @@
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
@@ -9631,15 +9631,15 @@
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
@@ -9705,154 +9705,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -9959,17 +9959,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -9978,6 +9967,17 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>2050</v>
+        <v>1850</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
@@ -10169,11 +10169,11 @@
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>2050</v>
+        <v>1850</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -10181,11 +10181,11 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>4050</v>
+        <v>3600</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>2116</v>
+        <v>1932</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>2950</v>
+        <v>2750</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>2861.5</v>
+        <v>2667.5</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -10268,11 +10268,11 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>4861.5</v>
+        <v>4417.5</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>3050</v>
+        <v>2850</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>2714.5</v>
+        <v>2536.5</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
@@ -10343,11 +10343,11 @@
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -10355,11 +10355,11 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>5619</v>
+        <v>5181</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>3268</v>
+        <v>3096</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>4750</v>
+        <v>4550</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
@@ -10430,11 +10430,11 @@
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>4322.5</v>
+        <v>4140.5</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -10442,11 +10442,11 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>6322.5</v>
+        <v>5890.5</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>4550</v>
+        <v>4350</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>3776.5000000000005</v>
+        <v>3610.5000000000005</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>5650</v>
+        <v>5450</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
@@ -10517,11 +10517,11 @@
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>4972</v>
+        <v>4796</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -10529,11 +10529,11 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>6972</v>
+        <v>6546</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>4240</v>
+        <v>4080</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -10733,23 +10733,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>102.5</v>
+        <v>92.5</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>147.5</v>
+        <v>137.5</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>237.5</v>
+        <v>227.5</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>282.5</v>
+        <v>272.5</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -10774,23 +10774,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>293.23</v>
+        <v>273.35000000000002</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>466.45000000000005</v>
+        <v>446.81</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>551.44000000000005</v>
+        <v>531.92000000000007</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -10815,23 +10815,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>307.5</v>
+        <v>277.5</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>436.30499999999995</v>
+        <v>406.72500000000002</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>682.57500000000005</v>
+        <v>653.83500000000004</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>800.04</v>
+        <v>771.72</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -10856,23 +10856,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>579.38000000000011</v>
+        <v>540.1</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>898.7</v>
+        <v>860.86</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>1048.6400000000001</v>
+        <v>1011.5200000000001</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -10897,23 +10897,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>512.5</v>
+        <v>462.49999999999994</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>722.45499999999993</v>
+        <v>673.47499999999991</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>1114.8249999999998</v>
+        <v>1067.885</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>1297.2399999999998</v>
+        <v>1251.32</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -10938,23 +10938,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>615</v>
+        <v>555</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>865.53</v>
+        <v>806.84999999999991</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>1330.9499999999998</v>
+        <v>1274.9099999999999</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1545.84</v>
+        <v>1491.12</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -10979,23 +10979,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>717.49999999999989</v>
+        <v>647.5</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>1008.6049999999999</v>
+        <v>940.22499999999991</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>1285.1299999999999</v>
+        <v>1218.3699999999999</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1547.0749999999998</v>
+        <v>1481.9349999999999</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1794.4399999999998</v>
+        <v>1730.9199999999998</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -11020,23 +11020,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>920.00000000000011</v>
+        <v>827.50000000000011</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>1251.68</v>
+        <v>1161.0999999999999</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>1566.08</v>
+        <v>1477.42</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1863.2</v>
+        <v>1776.46</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>2143.04</v>
+        <v>2058.2200000000003</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -11061,23 +11061,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>1122.5</v>
+        <v>1007.5</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>1494.7549999999999</v>
+        <v>1381.9749999999999</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1847.03</v>
+        <v>1736.47</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>2179.3250000000003</v>
+        <v>2070.9850000000001</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>2491.64</v>
+        <v>2385.52</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -11102,23 +11102,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>1325</v>
+        <v>1187.5</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>1737.83</v>
+        <v>1602.85</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>2127.98</v>
+        <v>1995.52</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>2495.4499999999998</v>
+        <v>2365.5100000000002</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>2840.24</v>
+        <v>2712.8199999999997</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -11143,23 +11143,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>1527.5</v>
+        <v>1367.5</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>1980.9050000000002</v>
+        <v>1823.7250000000004</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>2408.9300000000003</v>
+        <v>2254.5700000000002</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>2811.5749999999998</v>
+        <v>2660.0349999999999</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>3188.84</v>
+        <v>3040.1200000000003</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -11184,23 +11184,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>1730</v>
+        <v>1547.5</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>2223.98</v>
+        <v>2044.6000000000001</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>2689.88</v>
+        <v>2513.62</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>3127.7000000000003</v>
+        <v>2954.56</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>3537.44</v>
+        <v>3367.42</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -11225,23 +11225,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>1932.5000000000005</v>
+        <v>1727.5000000000005</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>2467.0550000000003</v>
+        <v>2265.4750000000004</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>2970.8300000000004</v>
+        <v>2772.67</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>3443.8250000000003</v>
+        <v>3249.085</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>3886.0400000000004</v>
+        <v>3694.7200000000003</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -11266,23 +11266,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>2135</v>
+        <v>1907.5</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>2710.13</v>
+        <v>2486.35</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>3251.78</v>
+        <v>3031.72</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>3759.95</v>
+        <v>3543.61</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>4234.6399999999994</v>
+        <v>4022.02</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -11307,23 +11307,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>2337.5</v>
+        <v>2087.5</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>2953.2049999999999</v>
+        <v>2707.2250000000004</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>3532.73</v>
+        <v>3290.77</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>4076.0750000000003</v>
+        <v>3838.1350000000002</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>4583.24</v>
+        <v>4349.32</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -11348,23 +11348,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>2540.0000000000005</v>
+        <v>2267.5000000000005</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>3196.28</v>
+        <v>2928.1000000000004</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>3813.6800000000003</v>
+        <v>3549.82</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>4392.2000000000007</v>
+        <v>4132.6600000000008</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>4931.8400000000011</v>
+        <v>4676.6200000000008</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -11389,23 +11389,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>2742.5</v>
+        <v>2447.5</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>3439.355</v>
+        <v>3148.9749999999999</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>4094.63</v>
+        <v>3808.87</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>4708.3250000000007</v>
+        <v>4427.1849999999995</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>5280.4400000000005</v>
+        <v>5003.92</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -11430,23 +11430,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>2945</v>
+        <v>2627.5000000000005</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>3682.4300000000003</v>
+        <v>3369.8500000000004</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>4375.58</v>
+        <v>4067.92</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>5024.4500000000007</v>
+        <v>4721.71</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>5629.0400000000009</v>
+        <v>5331.22</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -11471,23 +11471,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>3147.5</v>
+        <v>2807.5</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>3925.5050000000001</v>
+        <v>3590.7249999999999</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>4656.5300000000007</v>
+        <v>4326.9699999999993</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>5340.5749999999998</v>
+        <v>5016.2350000000006</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>5977.64</v>
+        <v>5658.5199999999995</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -11512,23 +11512,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>3350</v>
+        <v>2987.5</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>4168.58</v>
+        <v>3811.6</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>4937.4799999999996</v>
+        <v>4586.0200000000004</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>5656.7000000000007</v>
+        <v>5310.76</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>6326.24</v>
+        <v>5985.8200000000006</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
@@ -11859,11 +11859,11 @@
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
@@ -11871,11 +11871,11 @@
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>4119</v>
+        <v>3681</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>2116</v>
+        <v>1932</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -11933,7 +11933,7 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
@@ -11945,11 +11945,11 @@
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
@@ -11957,11 +11957,11 @@
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>4869</v>
+        <v>4431</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>3050</v>
+        <v>2850</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>2714.5</v>
+        <v>2536.5</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
@@ -12031,11 +12031,11 @@
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -12043,11 +12043,11 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>5619</v>
+        <v>5181</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>3268</v>
+        <v>3096</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
@@ -12117,11 +12117,11 @@
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
@@ -12129,11 +12129,11 @@
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>6369</v>
+        <v>5931</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>4550</v>
+        <v>4350</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>3776.5000000000005</v>
+        <v>3610.5000000000005</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
@@ -12203,11 +12203,11 @@
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3500</v>
+        <v>3250</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
@@ -12215,11 +12215,11 @@
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>7119</v>
+        <v>6681</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>4240</v>
+        <v>4080</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -12413,23 +12413,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -12453,23 +12453,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -12493,23 +12493,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -12533,23 +12533,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -12573,23 +12573,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -12613,23 +12613,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -12653,23 +12653,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>1290.1299999999999</v>
+        <v>1220.8699999999999</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>1291.3799999999999</v>
+        <v>1223.3699999999999</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>1285.1299999999999</v>
+        <v>1218.3699999999999</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>1285.1299999999999</v>
+        <v>1218.3699999999999</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>1285.1299999999999</v>
+        <v>1218.3699999999999</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -12693,23 +12693,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>1496.08</v>
+        <v>1404.92</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>1534.83</v>
+        <v>1444.92</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>1566.08</v>
+        <v>1477.42</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>1589.83</v>
+        <v>1502.42</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>1606.08</v>
+        <v>1519.92</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -12733,23 +12733,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1702.03</v>
+        <v>1588.97</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1778.28</v>
+        <v>1666.47</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1847.03</v>
+        <v>1736.47</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1908.28</v>
+        <v>1798.97</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1962.0300000000002</v>
+        <v>1853.97</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -12773,23 +12773,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1907.98</v>
+        <v>1773.02</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>2021.73</v>
+        <v>1888.02</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>2127.98</v>
+        <v>1995.52</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>2226.73</v>
+        <v>2095.52</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>2317.98</v>
+        <v>2188.02</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -12813,23 +12813,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>2113.9300000000003</v>
+        <v>1957.0700000000002</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>2265.1800000000003</v>
+        <v>2109.5700000000002</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>2408.9300000000003</v>
+        <v>2254.5700000000002</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>2545.1800000000003</v>
+        <v>2392.0700000000002</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>2673.9300000000003</v>
+        <v>2522.0700000000006</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -12853,23 +12853,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>2319.88</v>
+        <v>2141.12</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>2508.63</v>
+        <v>2331.12</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>2689.88</v>
+        <v>2513.62</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>2863.63</v>
+        <v>2688.62</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>3029.88</v>
+        <v>2856.12</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -12893,23 +12893,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>2525.8300000000004</v>
+        <v>2325.17</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>2752.0800000000004</v>
+        <v>2552.67</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>2970.8300000000004</v>
+        <v>2772.67</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>3182.0800000000004</v>
+        <v>2985.17</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>3385.8300000000004</v>
+        <v>3190.17</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -12933,23 +12933,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>2731.78</v>
+        <v>2509.2199999999998</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>2995.53</v>
+        <v>2774.22</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>3251.78</v>
+        <v>3031.72</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>3500.53</v>
+        <v>3281.72</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>3741.78</v>
+        <v>3524.22</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -12973,23 +12973,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>2937.73</v>
+        <v>2693.27</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>3238.98</v>
+        <v>2995.77</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>3532.73</v>
+        <v>3290.77</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>3818.98</v>
+        <v>3578.27</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>4097.7299999999996</v>
+        <v>3858.27</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -13013,23 +13013,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>3143.6800000000003</v>
+        <v>2877.32</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>3482.4300000000003</v>
+        <v>3217.32</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>3813.6800000000003</v>
+        <v>3549.82</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>4137.43</v>
+        <v>3874.8200000000006</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>4453.68</v>
+        <v>4192.3200000000006</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -13053,23 +13053,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>3349.63</v>
+        <v>3061.37</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>3725.88</v>
+        <v>3438.87</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>4094.63</v>
+        <v>3808.87</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>4455.88</v>
+        <v>4171.37</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>4809.63</v>
+        <v>4526.37</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -13093,23 +13093,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>3555.5800000000004</v>
+        <v>3245.42</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>3969.3300000000004</v>
+        <v>3660.42</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>4375.58</v>
+        <v>4067.92</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>4774.33</v>
+        <v>4467.92</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>5165.5800000000008</v>
+        <v>4860.42</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -13133,23 +13133,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>3761.53</v>
+        <v>3429.47</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>4212.7800000000007</v>
+        <v>3881.97</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>4656.5300000000007</v>
+        <v>4326.9699999999993</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>5092.7800000000007</v>
+        <v>4764.4699999999993</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>5521.5300000000007</v>
+        <v>5194.4699999999993</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -13173,23 +13173,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>3967.48</v>
+        <v>3613.52</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>4456.2299999999996</v>
+        <v>4103.5200000000004</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>4937.4799999999996</v>
+        <v>4586.0200000000004</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>5411.23</v>
+        <v>5061.0200000000004</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>5877.48</v>
+        <v>5528.52</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -13500,47 +13500,47 @@
       </c>
       <c r="F85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>1971</v>
+        <v>1850</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1971</v>
+        <v>2100</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>3250</v>
+        <v>2100</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="O85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>2210</v>
+        <v>1932</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -13586,47 +13586,47 @@
       </c>
       <c r="F86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>3600</v>
+        <v>2750</v>
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.71</v>
+        <v>0.97</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>2556</v>
+        <v>2667.5</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.6</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>2556</v>
+        <v>3667.5</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>4000</v>
+        <v>2850</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.215</v>
+        <v>0.24</v>
       </c>
       <c r="O86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>2600</v>
+        <v>2536.5</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -13672,47 +13672,47 @@
       </c>
       <c r="F87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>4500</v>
+        <v>3650</v>
       </c>
       <c r="G87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I87" s="8">
         <f>F87*H87</f>
-        <v>3104.9999999999995</v>
+        <v>3431</v>
       </c>
       <c r="J87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="K87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L87" s="8">
         <f>I87+J87</f>
-        <v>3104.9999999999995</v>
+        <v>5181</v>
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>4750</v>
+        <v>3600</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>2945</v>
+        <v>3096</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -13758,47 +13758,47 @@
       </c>
       <c r="F88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>5400</v>
+        <v>4550</v>
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.66999999999999993</v>
+        <v>0.90999999999999992</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>3617.9999999999995</v>
+        <v>4140.5</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.6</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>3617.9999999999995</v>
+        <v>6640.5</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>5500</v>
+        <v>4350</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.22500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="O88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.59000000000000008</v>
+        <v>0.83000000000000007</v>
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>3245.0000000000005</v>
+        <v>3610.5000000000005</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -13844,47 +13844,47 @@
       </c>
       <c r="F89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>6300</v>
+        <v>5450</v>
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>4095</v>
+        <v>4796</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>0</v>
+        <v>3250</v>
       </c>
       <c r="K89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>4095</v>
+        <v>8046</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>6250</v>
+        <v>5100</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="O89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.56000000000000005</v>
+        <v>0.8</v>
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>3500.0000000000005</v>
+        <v>4080</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -14066,23 +14066,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>162.5</v>
+        <v>105</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>200</v>
+        <v>142.5</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>237.5</v>
+        <v>180</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>275</v>
+        <v>217.5</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>312.5</v>
+        <v>255</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -14106,23 +14106,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>400</v>
+        <v>285</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>475</v>
+        <v>360</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>550</v>
+        <v>435</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>625</v>
+        <v>510</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -14146,23 +14146,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>487.5</v>
+        <v>315</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>600</v>
+        <v>427.5</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>712.5</v>
+        <v>540</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>825</v>
+        <v>652.5</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>937.5</v>
+        <v>765</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -14186,23 +14186,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>800</v>
+        <v>570</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>950</v>
+        <v>720</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>1100</v>
+        <v>870</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>1250</v>
+        <v>1020</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -14226,23 +14226,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>770.9</v>
+        <v>521.64</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>951</v>
+        <v>709.36500000000001</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>1133.3499999999999</v>
+        <v>900</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>1318.625</v>
+        <v>1087.5</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>1507.5</v>
+        <v>1275</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -14266,23 +14266,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>881.4</v>
+        <v>618.24</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>1081</v>
+        <v>836.19</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>1280.5999999999999</v>
+        <v>1054.8</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>1480.875</v>
+        <v>1275.42</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>1682.5</v>
+        <v>1499.3999999999999</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -14306,23 +14306,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>991.9</v>
+        <v>714.83999999999992</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>1211</v>
+        <v>963.01499999999999</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>1427.85</v>
+        <v>1209.5999999999999</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>1643.125</v>
+        <v>1455.9449999999999</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1857.5</v>
+        <v>1703.3999999999999</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -14346,23 +14346,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>1102.4000000000001</v>
+        <v>811.44</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>1341</v>
+        <v>1089.8400000000001</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>1575.1</v>
+        <v>1364.4</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>1805.375</v>
+        <v>1636.47</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>2032.5</v>
+        <v>1907.4</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -14386,23 +14386,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>1212.9000000000001</v>
+        <v>908.04</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>1471</v>
+        <v>1216.665</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>1722.35</v>
+        <v>1519.2</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1967.625</v>
+        <v>1816.9950000000001</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>2207.5</v>
+        <v>2111.4</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -14426,23 +14426,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>1323.4</v>
+        <v>1004.64</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>1601</v>
+        <v>1343.49</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>1869.6</v>
+        <v>1674</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>2129.875</v>
+        <v>1997.52</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>2382.5</v>
+        <v>2315.4</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -14466,23 +14466,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>1433.9</v>
+        <v>1101.2400000000002</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>1731.0000000000002</v>
+        <v>1470.3150000000001</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>2016.8500000000004</v>
+        <v>1828.8000000000002</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>2292.1250000000005</v>
+        <v>2178.0450000000001</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>2557.5000000000005</v>
+        <v>2519.4</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -14506,23 +14506,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>1544.4</v>
+        <v>1197.8400000000001</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>1861</v>
+        <v>1597.1399999999999</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>2164.1</v>
+        <v>1983.6</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>2454.375</v>
+        <v>2358.5699999999997</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>2732.5</v>
+        <v>2723.3999999999996</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -14546,23 +14546,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>1654.9</v>
+        <v>1294.44</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>1991.0000000000002</v>
+        <v>1723.9650000000001</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>2311.3500000000004</v>
+        <v>2138.4</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>2616.625</v>
+        <v>2539.0950000000003</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>2907.5</v>
+        <v>2927.4</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -14586,23 +14586,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>1765.4</v>
+        <v>1391.04</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>2121</v>
+        <v>1850.79</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>2458.6</v>
+        <v>2293.1999999999998</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>2778.875</v>
+        <v>2719.62</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>3082.5</v>
+        <v>3131.3999999999996</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -14626,23 +14626,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>1875.9</v>
+        <v>1487.6399999999999</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>2251</v>
+        <v>1977.615</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>2605.8500000000004</v>
+        <v>2448</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>2941.125</v>
+        <v>2900.1450000000004</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>3257.5</v>
+        <v>3335.3999999999996</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -14666,23 +14666,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>1986.4</v>
+        <v>1584.24</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>2381</v>
+        <v>2104.44</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>2753.1000000000004</v>
+        <v>2602.8000000000002</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>3103.3750000000005</v>
+        <v>3080.67</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>3432.5000000000005</v>
+        <v>3539.4</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -14706,23 +14706,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>2096.9</v>
+        <v>1680.84</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>2511</v>
+        <v>2231.2649999999999</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>2900.35</v>
+        <v>2757.6</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>3265.625</v>
+        <v>3261.1950000000002</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>3607.5000000000005</v>
+        <v>3743.3999999999996</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -14746,23 +14746,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>2207.4</v>
+        <v>1777.44</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>2641</v>
+        <v>2358.09</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>3047.6000000000004</v>
+        <v>2912.4</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>3427.8750000000005</v>
+        <v>3441.7200000000003</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>3782.5000000000005</v>
+        <v>3947.4</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -14786,23 +14786,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>2317.9</v>
+        <v>1874.04</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>2771</v>
+        <v>2484.915</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>3194.85</v>
+        <v>3067.2</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>3590.1250000000005</v>
+        <v>3622.2450000000003</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>3957.5000000000005</v>
+        <v>4151.3999999999996</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -14826,23 +14826,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>2428.4</v>
+        <v>1970.64</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>2901</v>
+        <v>2611.7399999999998</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>3342.1</v>
+        <v>3222</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>3752.3750000000005</v>
+        <v>3802.7700000000004</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>4132.5</v>
+        <v>4355.3999999999996</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>2050</v>
+        <v>1850</v>
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
@@ -15165,11 +15165,11 @@
       </c>
       <c r="I125" s="8">
         <f>F125*H125</f>
-        <v>2050</v>
+        <v>1850</v>
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
@@ -15177,11 +15177,11 @@
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>2550</v>
+        <v>2100</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>2116</v>
+        <v>1932</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>2950</v>
+        <v>2750</v>
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
@@ -15251,11 +15251,11 @@
       </c>
       <c r="I126" s="8">
         <f>F126*H126</f>
-        <v>2861.5</v>
+        <v>2667.5</v>
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -15263,11 +15263,11 @@
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>4111.5</v>
+        <v>3667.5</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>3050</v>
+        <v>2850</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>2714.5</v>
+        <v>2536.5</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="F127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>3850</v>
+        <v>3650</v>
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
@@ -15337,11 +15337,11 @@
       </c>
       <c r="I127" s="8">
         <f>F127*H127</f>
-        <v>3619</v>
+        <v>3431</v>
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="K127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -15349,11 +15349,11 @@
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>5619</v>
+        <v>5181</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>3268</v>
+        <v>3096</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="F128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>4750</v>
+        <v>4550</v>
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
@@ -15423,11 +15423,11 @@
       </c>
       <c r="I128" s="8">
         <f>F128*H128</f>
-        <v>4322.5</v>
+        <v>4140.5</v>
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -15435,11 +15435,11 @@
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>7072.5</v>
+        <v>6640.5</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>4550</v>
+        <v>4350</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>3776.5000000000005</v>
+        <v>3610.5000000000005</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="F129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>5650</v>
+        <v>5450</v>
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
@@ -15509,11 +15509,11 @@
       </c>
       <c r="I129" s="8">
         <f>F129*H129</f>
-        <v>4972</v>
+        <v>4796</v>
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>3500</v>
+        <v>3250</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -15521,11 +15521,11 @@
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>8472</v>
+        <v>8046</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>4240</v>
+        <v>4080</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -15749,43 +15749,43 @@
       </c>
       <c r="C135" s="15">
         <f t="shared" si="15"/>
-        <v>102.5</v>
+        <v>92.5</v>
       </c>
       <c r="D135" s="15">
         <f t="shared" si="16"/>
-        <v>147.5</v>
+        <v>137.5</v>
       </c>
       <c r="E135" s="15">
         <f t="shared" si="17"/>
-        <v>192.5</v>
+        <v>182.5</v>
       </c>
       <c r="F135" s="15">
         <f t="shared" si="18"/>
-        <v>237.5</v>
+        <v>227.5</v>
       </c>
       <c r="G135" s="15">
         <f t="shared" si="19"/>
-        <v>282.5</v>
+        <v>272.5</v>
       </c>
       <c r="H135" s="15">
         <f t="shared" si="20"/>
-        <v>-115</v>
+        <v>-105</v>
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-152.5</v>
+        <v>-142.5</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
-        <v>-190</v>
+        <v>-180</v>
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-227.5</v>
+        <v>-217.5</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-265</v>
+        <v>-255</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -15804,43 +15804,43 @@
       </c>
       <c r="C136" s="15">
         <f t="shared" si="15"/>
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D136" s="15">
         <f t="shared" si="16"/>
-        <v>293.23</v>
+        <v>273.35000000000002</v>
       </c>
       <c r="E136" s="15">
         <f t="shared" si="17"/>
-        <v>380.38</v>
+        <v>360.62</v>
       </c>
       <c r="F136" s="15">
         <f t="shared" si="18"/>
-        <v>466.45000000000005</v>
+        <v>446.81</v>
       </c>
       <c r="G136" s="15">
         <f t="shared" si="19"/>
-        <v>551.44000000000005</v>
+        <v>531.92000000000007</v>
       </c>
       <c r="H136" s="15">
         <f t="shared" si="20"/>
-        <v>-230</v>
+        <v>-210</v>
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-305</v>
+        <v>-285</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
-        <v>-380</v>
+        <v>-360</v>
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-455</v>
+        <v>-435</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-530</v>
+        <v>-510</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -15859,43 +15859,43 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>307.5</v>
+        <v>277.5</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>436.30499999999995</v>
+        <v>406.72500000000002</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>561.32999999999993</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>682.57500000000005</v>
+        <v>653.83500000000004</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>800.04</v>
+        <v>771.72</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
-        <v>-345</v>
+        <v>-315</v>
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-457.5</v>
+        <v>-427.5</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
-        <v>-570</v>
+        <v>-540</v>
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-682.5</v>
+        <v>-652.5</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-795</v>
+        <v>-765</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -15914,43 +15914,43 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>579.38000000000011</v>
+        <v>540.1</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>742.28</v>
+        <v>703.72</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>898.7</v>
+        <v>860.86</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>1048.6400000000001</v>
+        <v>1011.5200000000001</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
-        <v>-460</v>
+        <v>-420</v>
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-610</v>
+        <v>-570</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
-        <v>-760</v>
+        <v>-720</v>
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-910</v>
+        <v>-870</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-1060</v>
+        <v>-1020</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -15969,43 +15969,43 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>512.5</v>
+        <v>462.49999999999994</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>722.45499999999993</v>
+        <v>673.47499999999991</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>923.2299999999999</v>
+        <v>875.27</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>1114.8249999999998</v>
+        <v>1067.885</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>1297.2399999999998</v>
+        <v>1251.32</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-571.31999999999994</v>
+        <v>-521.64</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-759.14499999999998</v>
+        <v>-709.36500000000001</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
-        <v>-950</v>
+        <v>-900</v>
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-1137.5</v>
+        <v>-1087.5</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-1325</v>
+        <v>-1275</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -16024,43 +16024,43 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>615</v>
+        <v>555</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>865.53</v>
+        <v>806.84999999999991</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>1104.1799999999998</v>
+        <v>1046.82</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>1330.9499999999998</v>
+        <v>1274.9099999999999</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1545.84</v>
+        <v>1491.12</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-677.11999999999989</v>
+        <v>-618.24</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-894.87</v>
+        <v>-836.19</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-1113.4000000000001</v>
+        <v>-1054.8</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-1334.06</v>
+        <v>-1275.42</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-1558.1999999999998</v>
+        <v>-1499.3999999999999</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -16079,43 +16079,43 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>722.49999999999989</v>
+        <v>650</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>1014.8549999999999</v>
+        <v>945.22499999999991</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>1285.1299999999999</v>
+        <v>1218.3699999999999</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1547.0749999999998</v>
+        <v>1481.9349999999999</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>1794.4399999999998</v>
+        <v>1730.9199999999998</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-782.92</v>
+        <v>-714.83999999999992</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-1030.595</v>
+        <v>-963.01499999999999</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-1276.8</v>
+        <v>-1209.5999999999999</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-1522.885</v>
+        <v>-1455.9449999999999</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1770.1999999999998</v>
+        <v>-1703.3999999999999</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -16134,43 +16134,43 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>850</v>
+        <v>755</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>1220.43</v>
+        <v>1128.5999999999999</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>1566.08</v>
+        <v>1477.42</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>1886.9500000000003</v>
+        <v>1801.46</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>2183.04</v>
+        <v>2100.7200000000003</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-888.72</v>
+        <v>-811.44</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-1166.3200000000002</v>
+        <v>-1089.8400000000001</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-1440.2</v>
+        <v>-1364.4</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-1711.71</v>
+        <v>-1636.47</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1982.2</v>
+        <v>-1907.4</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -16189,43 +16189,43 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>977.5</v>
+        <v>860</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>1426.0049999999999</v>
+        <v>1311.9749999999999</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>1847.03</v>
+        <v>1736.47</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>2240.5750000000003</v>
+        <v>2133.4850000000001</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>2606.64</v>
+        <v>2503.02</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-994.52</v>
+        <v>-908.04</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-1302.0450000000001</v>
+        <v>-1216.665</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-1603.6</v>
+        <v>-1519.2</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1900.5350000000001</v>
+        <v>-1816.9950000000001</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-2194.1999999999998</v>
+        <v>-2111.4</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -16244,43 +16244,43 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>1105</v>
+        <v>965</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>1631.58</v>
+        <v>1495.35</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>2127.98</v>
+        <v>1995.52</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>2594.1999999999998</v>
+        <v>2465.5100000000002</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>3030.24</v>
+        <v>2905.3199999999997</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-1100.3200000000002</v>
+        <v>-1004.64</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-1437.77</v>
+        <v>-1343.49</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-1767</v>
+        <v>-1674</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-2089.36</v>
+        <v>-1997.52</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-2406.1999999999998</v>
+        <v>-2315.4</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -16299,43 +16299,43 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>1232.5</v>
+        <v>1070</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>1837.1550000000002</v>
+        <v>1678.7250000000001</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>2408.9300000000003</v>
+        <v>2254.5700000000002</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>2947.8249999999998</v>
+        <v>2797.5349999999999</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>3453.84</v>
+        <v>3307.6200000000008</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-1206.1200000000001</v>
+        <v>-1101.2400000000002</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-1573.4950000000001</v>
+        <v>-1470.3150000000001</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-1930.4</v>
+        <v>-1828.8000000000002</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-2278.1850000000004</v>
+        <v>-2178.0450000000001</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-2618.1999999999998</v>
+        <v>-2519.4</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -16354,43 +16354,43 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>1360</v>
+        <v>1175</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>2042.73</v>
+        <v>1862.1000000000001</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>2689.88</v>
+        <v>2513.62</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>3301.4500000000003</v>
+        <v>3129.56</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>3877.44</v>
+        <v>3709.92</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-1311.92</v>
+        <v>-1197.8400000000001</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-1709.2199999999998</v>
+        <v>-1597.1399999999999</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-2093.8000000000002</v>
+        <v>-1983.6</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-2467.0100000000002</v>
+        <v>-2358.5699999999997</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-2830.2</v>
+        <v>-2723.3999999999996</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -16409,43 +16409,43 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>1487.5000000000002</v>
+        <v>1280.0000000000002</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>2248.3050000000003</v>
+        <v>2045.4750000000001</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>2970.8300000000004</v>
+        <v>2772.67</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>3655.0750000000003</v>
+        <v>3461.585</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>4301.0400000000009</v>
+        <v>4112.22</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-1417.7200000000003</v>
+        <v>-1294.44</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-1844.9450000000002</v>
+        <v>-1723.9650000000001</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-2257.1999999999998</v>
+        <v>-2138.4</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-2655.835</v>
+        <v>-2539.0950000000003</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-3042.2</v>
+        <v>-2927.4</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -16464,43 +16464,43 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>1615</v>
+        <v>1385</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>2453.88</v>
+        <v>2228.85</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>3251.78</v>
+        <v>3031.72</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>4008.7</v>
+        <v>3793.61</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>4724.6399999999994</v>
+        <v>4514.5200000000004</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-1523.52</v>
+        <v>-1391.04</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-1980.6699999999998</v>
+        <v>-1850.79</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-2420.6</v>
+        <v>-2293.1999999999998</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-2844.66</v>
+        <v>-2719.62</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-3254.2</v>
+        <v>-3131.3999999999996</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -16519,43 +16519,43 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>1742.5</v>
+        <v>1490</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>2659.4549999999999</v>
+        <v>2412.2250000000004</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>3532.73</v>
+        <v>3290.77</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>4362.3250000000007</v>
+        <v>4125.6350000000002</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>5148.24</v>
+        <v>4916.82</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-1629.32</v>
+        <v>-1487.6399999999999</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-2116.395</v>
+        <v>-1977.615</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-2584</v>
+        <v>-2448</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-3033.4850000000001</v>
+        <v>-2900.1450000000004</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-3466.2</v>
+        <v>-3335.3999999999996</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -16574,43 +16574,43 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>1870.0000000000002</v>
+        <v>1595.0000000000002</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>2865.03</v>
+        <v>2595.6000000000004</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>3813.6800000000003</v>
+        <v>3549.82</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>4715.9500000000007</v>
+        <v>4457.6600000000008</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>5571.8400000000011</v>
+        <v>5319.1200000000008</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-1735.1200000000001</v>
+        <v>-1584.24</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-2252.12</v>
+        <v>-2104.44</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-2747.4</v>
+        <v>-2602.8000000000002</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-3222.3100000000004</v>
+        <v>-3080.67</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-3678.2000000000003</v>
+        <v>-3539.4</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -16629,43 +16629,43 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>1997.5</v>
+        <v>1700</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>3070.605</v>
+        <v>2778.9749999999999</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>4094.63</v>
+        <v>3808.87</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>5069.5750000000007</v>
+        <v>4789.6849999999995</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>5995.4400000000005</v>
+        <v>5721.42</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-1840.92</v>
+        <v>-1680.84</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-2387.8450000000003</v>
+        <v>-2231.2649999999999</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-2910.8</v>
+        <v>-2757.6</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-3411.1350000000002</v>
+        <v>-3261.1950000000002</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-3890.2</v>
+        <v>-3743.3999999999996</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -16684,43 +16684,43 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>2125</v>
+        <v>1805.0000000000002</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>3276.1800000000003</v>
+        <v>2962.3500000000004</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>4375.58</v>
+        <v>4067.92</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>5423.2000000000007</v>
+        <v>5121.71</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>6419.0400000000009</v>
+        <v>6123.72</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-1946.72</v>
+        <v>-1777.44</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-2523.5700000000002</v>
+        <v>-2358.09</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-3074.2000000000003</v>
+        <v>-2912.4</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-3599.9600000000005</v>
+        <v>-3441.7200000000003</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-4102.2</v>
+        <v>-3947.4</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -16739,43 +16739,43 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>2252.5</v>
+        <v>1910</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>3481.7550000000001</v>
+        <v>3145.7249999999999</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>4656.5300000000007</v>
+        <v>4326.9699999999993</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>5776.8249999999998</v>
+        <v>5453.7350000000006</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>6842.64</v>
+        <v>6526.0199999999995</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-2052.52</v>
+        <v>-1874.04</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-2659.2950000000001</v>
+        <v>-2484.915</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-3237.6</v>
+        <v>-3067.2</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-3788.7850000000003</v>
+        <v>-3622.2450000000003</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-4314.2</v>
+        <v>-4151.3999999999996</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -16794,43 +16794,43 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>2380</v>
+        <v>2015</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>3687.33</v>
+        <v>3329.1</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>4937.4799999999996</v>
+        <v>4586.0200000000004</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>6130.4500000000007</v>
+        <v>5785.76</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>7266.24</v>
+        <v>6928.3200000000006</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-2158.3199999999997</v>
+        <v>-1970.64</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-2795.02</v>
+        <v>-2611.7399999999998</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-3401</v>
+        <v>-3222</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-3977.61</v>
+        <v>-3802.7700000000004</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-4526.2</v>
+        <v>-4355.3999999999996</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>
@@ -17017,47 +17017,47 @@
       </c>
       <c r="F165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q165)+(INDEX(Parameters!$J$10:$N$10,1,Q165+1)-INDEX(Parameters!$J$10:$N$10,1,Q165))*T165,INDEX(Parameters!$D$10:$H$10,1,Q165)+(INDEX(Parameters!$D$10:$H$10,1,Q165+1)-INDEX(Parameters!$D$10:$H$10,1,Q165))*T165)</f>
-        <v>4500</v>
+        <v>3650</v>
       </c>
       <c r="G165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R165)+(INDEX(Parameters!$J$11:$N$11,1,R165+1)-INDEX(Parameters!$J$11:$N$11,1,R165))*U165,INDEX(Parameters!$D$11:$H$11,1,Q165)+(INDEX(Parameters!$D$11:$H$11,1,Q165+1)-INDEX(Parameters!$D$11:$H$11,1,Q165))*T165)</f>
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="H165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q165)+(INDEX(Parameters!$J$12:$N$12,1,Q165+1)-INDEX(Parameters!$J$12:$N$12,1,Q165))*T165,INDEX(Parameters!$D$12:$H$12,1,Q165)+(INDEX(Parameters!$D$12:$H$12,1,Q165+1)-INDEX(Parameters!$D$12:$H$12,1,Q165))*T165)</f>
-        <v>0.69</v>
+        <v>0.94</v>
       </c>
       <c r="I165">
         <f>F165*H165</f>
-        <v>3104.9999999999995</v>
+        <v>3431</v>
       </c>
       <c r="J165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="K165">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L165">
         <f>I165+J165</f>
-        <v>3104.9999999999995</v>
+        <v>5181</v>
       </c>
       <c r="M165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>
-        <v>4750</v>
+        <v>3600</v>
       </c>
       <c r="N165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="O165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S165)+(INDEX(Parameters!$J$19:$N$19,1,S165+1)-INDEX(Parameters!$J$19:$N$19,1,S165))*V165,INDEX(Parameters!$D$19:$H$19,1,S165)+(INDEX(Parameters!$D$19:$H$19,1,S165+1)-INDEX(Parameters!$D$19:$H$19,1,S165))*V165)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P165">
         <f>M165*O165</f>
-        <v>2945</v>
+        <v>3096</v>
       </c>
       <c r="Q165">
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>

--- a/docs/damping_curve_MRAx0.xlsx
+++ b/docs/damping_curve_MRAx0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61CA6CC-DDCF-4DFA-8B8D-8D400F134D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C68EC0-C45A-40FC-B563-259B7187135E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -491,20 +491,23 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -512,11 +515,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1506,40 +1506,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.5</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360.62</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>532.16999999999996</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703.72</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.27</c:v>
+                  <c:v>984.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1046.82</c:v>
+                  <c:v>1129.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1220.8699999999999</c:v>
+                  <c:v>1274.6999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1404.92</c:v>
+                  <c:v>1419.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1588.97</c:v>
+                  <c:v>1564.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1773.02</c:v>
+                  <c:v>1709.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1957.0700000000002</c:v>
+                  <c:v>1854.3000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2141.12</c:v>
+                  <c:v>1999.1999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1634,40 +1634,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.5</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360.62</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>532.16999999999996</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703.72</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.27</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1046.82</c:v>
+                  <c:v>1194.9000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1223.3699999999999</c:v>
+                  <c:v>1339.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1444.92</c:v>
+                  <c:v>1484.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1666.47</c:v>
+                  <c:v>1629.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1888.02</c:v>
+                  <c:v>1774.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2109.5700000000002</c:v>
+                  <c:v>1919.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2331.12</c:v>
+                  <c:v>2064.3000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,40 +1762,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.5</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360.62</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>532.16999999999996</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703.72</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.27</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1046.82</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1218.3699999999999</c:v>
+                  <c:v>1404.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1477.42</c:v>
+                  <c:v>1549.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1736.47</c:v>
+                  <c:v>1694.7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1995.52</c:v>
+                  <c:v>1839.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2254.5700000000002</c:v>
+                  <c:v>1984.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2513.62</c:v>
+                  <c:v>2129.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1890,40 +1890,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.5</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360.62</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>532.16999999999996</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703.72</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.27</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1046.82</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1218.3699999999999</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1502.42</c:v>
+                  <c:v>1614.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1798.97</c:v>
+                  <c:v>1759.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2095.52</c:v>
+                  <c:v>1904.7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2392.0700000000002</c:v>
+                  <c:v>2049.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2688.62</c:v>
+                  <c:v>2194.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,40 +2018,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>182.5</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360.62</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>532.16999999999996</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>703.72</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875.27</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1046.82</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1218.3699999999999</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1519.92</c:v>
+                  <c:v>1680</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1853.97</c:v>
+                  <c:v>1824.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2188.02</c:v>
+                  <c:v>1969.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2522.0700000000006</c:v>
+                  <c:v>2114.6999999999998</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2856.12</c:v>
+                  <c:v>2259.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="20"/>
@@ -4977,17 +4977,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -5018,13 +5018,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
-      <c r="I8" s="26">
+      <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1736.47</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="24"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -5114,11 +5114,11 @@
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="26">
+      <c r="I10" s="24">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -5170,13 +5170,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -5484,20 +5484,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -5758,17 +5758,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -5776,6 +5765,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -5836,7 +5836,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>75</v>
       </c>
       <c r="C2" s="20"/>
@@ -5879,17 +5879,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6513,20 +6513,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>77</v>
       </c>
       <c r="C2" s="20"/>
@@ -6640,20 +6640,20 @@
         <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7277,20 +7277,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7364,7 +7364,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="20"/>
@@ -7407,17 +7407,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8037,20 +8037,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8120,7 +8120,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="20"/>
@@ -8163,17 +8163,17 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8793,20 +8793,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>62</v>
       </c>
       <c r="C2" s="20"/>
@@ -8899,7 +8899,7 @@
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>85</v>
       </c>
       <c r="C3" s="20"/>
@@ -8937,21 +8937,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -9581,21 +9581,21 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
@@ -9608,17 +9608,17 @@
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
@@ -9631,15 +9631,15 @@
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
@@ -9705,154 +9705,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -9959,6 +9959,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -9967,17 +9978,6 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11847,47 +11847,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.94</v>
+        <v>0.69</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>3431</v>
+        <v>2898</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.34</v>
+        <v>0.6</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>3681</v>
+        <v>2898</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.92</v>
+        <v>0.68</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>1932</v>
+        <v>2040.0000000000002</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -11933,47 +11933,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.94</v>
+        <v>0.69</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>3431</v>
+        <v>2898</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.34499999999999997</v>
+        <v>0.6</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>4431</v>
+        <v>2898</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>2850</v>
+        <v>3750</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.24</v>
+        <v>0.215</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>2536.5</v>
+        <v>2437.5</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -12019,47 +12019,47 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.94</v>
+        <v>0.69</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>3431</v>
+        <v>2898</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>1750</v>
+        <v>0</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>5181</v>
+        <v>2898</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>3096</v>
+        <v>2790</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -12105,47 +12105,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.94</v>
+        <v>0.69</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>3431</v>
+        <v>2898</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.35499999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>5931</v>
+        <v>2898</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>4350</v>
+        <v>5250</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.26</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.83000000000000007</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>3610.5000000000005</v>
+        <v>3097.5000000000005</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -12191,47 +12191,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3650</v>
+        <v>4200</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.94</v>
+        <v>0.69</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>3431</v>
+        <v>2898</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3250</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>6681</v>
+        <v>2898</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>5100</v>
+        <v>6000</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.8</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>4080</v>
+        <v>3360.0000000000005</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -12413,23 +12413,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>182.5</v>
+        <v>210</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>182.5</v>
+        <v>210</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>182.5</v>
+        <v>210</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>182.5</v>
+        <v>210</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>182.5</v>
+        <v>210</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -12453,23 +12453,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>360.62</v>
+        <v>420</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>360.62</v>
+        <v>420</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>360.62</v>
+        <v>420</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>360.62</v>
+        <v>420</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>360.62</v>
+        <v>420</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -12493,23 +12493,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>532.16999999999996</v>
+        <v>630</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>532.16999999999996</v>
+        <v>630</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>532.16999999999996</v>
+        <v>630</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>532.16999999999996</v>
+        <v>630</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>532.16999999999996</v>
+        <v>630</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -12533,23 +12533,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>703.72</v>
+        <v>840</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>703.72</v>
+        <v>840</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>703.72</v>
+        <v>840</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>703.72</v>
+        <v>840</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>703.72</v>
+        <v>840</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -12573,23 +12573,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>875.27</v>
+        <v>984.9</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>875.27</v>
+        <v>1050</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>875.27</v>
+        <v>1050</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>875.27</v>
+        <v>1050</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>875.27</v>
+        <v>1050</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -12613,23 +12613,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>1046.82</v>
+        <v>1129.8</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>1046.82</v>
+        <v>1194.9000000000001</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>1046.82</v>
+        <v>1260</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>1046.82</v>
+        <v>1260</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>1046.82</v>
+        <v>1260</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -12653,23 +12653,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>1220.8699999999999</v>
+        <v>1274.6999999999998</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>1223.3699999999999</v>
+        <v>1339.8</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>1218.3699999999999</v>
+        <v>1404.9</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>1218.3699999999999</v>
+        <v>1470</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>1218.3699999999999</v>
+        <v>1470</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -12693,23 +12693,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>1404.92</v>
+        <v>1419.6</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>1444.92</v>
+        <v>1484.7</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>1477.42</v>
+        <v>1549.8000000000002</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>1502.42</v>
+        <v>1614.9</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>1519.92</v>
+        <v>1680</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -12733,23 +12733,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1588.97</v>
+        <v>1564.5</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1666.47</v>
+        <v>1629.6</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1736.47</v>
+        <v>1694.7</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1798.97</v>
+        <v>1759.8000000000002</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1853.97</v>
+        <v>1824.9</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -12773,23 +12773,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1773.02</v>
+        <v>1709.4</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1888.02</v>
+        <v>1774.5</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1995.52</v>
+        <v>1839.6</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>2095.52</v>
+        <v>1904.7</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>2188.02</v>
+        <v>1969.8</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -12813,23 +12813,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1957.0700000000002</v>
+        <v>1854.3000000000002</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>2109.5700000000002</v>
+        <v>1919.4</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>2254.5700000000002</v>
+        <v>1984.5</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>2392.0700000000002</v>
+        <v>2049.6000000000004</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>2522.0700000000006</v>
+        <v>2114.6999999999998</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -12853,23 +12853,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>2141.12</v>
+        <v>1999.1999999999998</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>2331.12</v>
+        <v>2064.3000000000002</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>2513.62</v>
+        <v>2129.4</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>2688.62</v>
+        <v>2194.5</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>2856.12</v>
+        <v>2259.6</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -12893,23 +12893,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>2325.17</v>
+        <v>2144.1000000000004</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>2552.67</v>
+        <v>2209.1999999999998</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>2772.67</v>
+        <v>2274.3000000000002</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>2985.17</v>
+        <v>2339.4</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>3190.17</v>
+        <v>2404.5</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -12933,23 +12933,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>2509.2199999999998</v>
+        <v>2289</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>2774.22</v>
+        <v>2354.1</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>3031.72</v>
+        <v>2419.1999999999998</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>3281.72</v>
+        <v>2484.3000000000002</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>3524.22</v>
+        <v>2549.3999999999996</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -12973,23 +12973,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>2693.27</v>
+        <v>2433.9</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>2995.77</v>
+        <v>2499</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>3290.77</v>
+        <v>2564.1000000000004</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>3578.27</v>
+        <v>2629.2</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>3858.27</v>
+        <v>2694.3</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -13013,23 +13013,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>2877.32</v>
+        <v>2578.8000000000002</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>3217.32</v>
+        <v>2643.9</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>3549.82</v>
+        <v>2709</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>3874.8200000000006</v>
+        <v>2774.1000000000004</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>4192.3200000000006</v>
+        <v>2839.2</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -13053,23 +13053,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>3061.37</v>
+        <v>2723.7</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>3438.87</v>
+        <v>2788.8</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>3808.87</v>
+        <v>2853.9</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>4171.37</v>
+        <v>2919</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>4526.37</v>
+        <v>2984.1</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -13093,23 +13093,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>3245.42</v>
+        <v>2868.6</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>3660.42</v>
+        <v>2933.7</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>4067.92</v>
+        <v>2998.8</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>4467.92</v>
+        <v>3063.9</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>4860.42</v>
+        <v>3129</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -13133,23 +13133,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>3429.47</v>
+        <v>3013.5</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>3881.97</v>
+        <v>3078.6</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>4326.9699999999993</v>
+        <v>3143.7</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>4764.4699999999993</v>
+        <v>3208.8</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>5194.4699999999993</v>
+        <v>3273.8999999999996</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -13173,23 +13173,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>3613.52</v>
+        <v>3158.4</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>4103.5200000000004</v>
+        <v>3223.5</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>4586.0200000000004</v>
+        <v>3288.6</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>5061.0200000000004</v>
+        <v>3353.7</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>5528.52</v>
+        <v>3418.8</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
